--- a/Bibsam_tidskriftslistor/scifree_data_wiley.xlsx
+++ b/Bibsam_tidskriftslistor/scifree_data_wiley.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\larher\Documents\GitHub\oa-tskr\Bibsam_tidskriftslistor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{242ED348-F32E-455A-9814-31DA63A518A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFDF401E-7426-4B12-B360-441250C2DECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{753E9841-99A9-44F0-9A7D-0846D9491BCF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12357" uniqueCount="6798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12351" uniqueCount="6795">
   <si>
     <t>Imprint</t>
   </si>
@@ -20421,15 +20421,6 @@
   </si>
   <si>
     <t>CC-BY-NC,CC-BY-NC-ND</t>
-  </si>
-  <si>
-    <t>2690-442X</t>
-  </si>
-  <si>
-    <t>Skin Health and Disease</t>
-  </si>
-  <si>
-    <t>https://onlinelibrary.wiley.com/journal/2690442x</t>
   </si>
 </sst>
 </file>
@@ -20485,8 +20476,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FD76128E-98FD-4771-BF79-D8900561C9C0}" name="Table1" displayName="Table1" ref="A1:G1860" totalsRowShown="0">
-  <autoFilter ref="A1:G1860" xr:uid="{FD76128E-98FD-4771-BF79-D8900561C9C0}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FD76128E-98FD-4771-BF79-D8900561C9C0}" name="Table1" displayName="Table1" ref="A1:G1859" totalsRowShown="0">
+  <autoFilter ref="A1:G1859" xr:uid="{FD76128E-98FD-4771-BF79-D8900561C9C0}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{4BE857EB-C270-4E18-8D6D-FDC0AAD7156C}" name="Imprint"/>
     <tableColumn id="2" xr3:uid="{DE86A7ED-73B1-4884-BCA4-B67A1150C6FF}" name="ISSN Electronic"/>
@@ -20797,7 +20788,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50476B14-7E66-4551-87E6-92F820F5A490}">
-  <dimension ref="A1:G1860"/>
+  <dimension ref="A1:G1859"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
@@ -56556,19 +56547,22 @@
         <v>7</v>
       </c>
       <c r="B1633" t="s">
-        <v>6795</v>
+        <v>5470</v>
+      </c>
+      <c r="C1633" t="s">
+        <v>5471</v>
       </c>
       <c r="D1633" t="s">
-        <v>6796</v>
+        <v>5472</v>
       </c>
       <c r="E1633" t="s">
-        <v>6797</v>
+        <v>5473</v>
       </c>
       <c r="F1633" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G1633" t="s">
-        <v>6257</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1634" spans="1:7" x14ac:dyDescent="0.25">
@@ -56576,16 +56570,13 @@
         <v>7</v>
       </c>
       <c r="B1634" t="s">
-        <v>5470</v>
-      </c>
-      <c r="C1634" t="s">
-        <v>5471</v>
+        <v>5474</v>
       </c>
       <c r="D1634" t="s">
-        <v>5472</v>
+        <v>5475</v>
       </c>
       <c r="E1634" t="s">
-        <v>5473</v>
+        <v>5476</v>
       </c>
       <c r="F1634" t="s">
         <v>12</v>
@@ -56599,19 +56590,22 @@
         <v>7</v>
       </c>
       <c r="B1635" t="s">
-        <v>5474</v>
+        <v>5466</v>
+      </c>
+      <c r="C1635" t="s">
+        <v>5467</v>
       </c>
       <c r="D1635" t="s">
-        <v>5475</v>
+        <v>5468</v>
       </c>
       <c r="E1635" t="s">
-        <v>5476</v>
+        <v>5469</v>
       </c>
       <c r="F1635" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G1635" t="s">
-        <v>13</v>
+        <v>6257</v>
       </c>
     </row>
     <row r="1636" spans="1:7" x14ac:dyDescent="0.25">
@@ -56619,16 +56613,13 @@
         <v>7</v>
       </c>
       <c r="B1636" t="s">
-        <v>5466</v>
-      </c>
-      <c r="C1636" t="s">
-        <v>5467</v>
+        <v>5477</v>
       </c>
       <c r="D1636" t="s">
-        <v>5468</v>
+        <v>5478</v>
       </c>
       <c r="E1636" t="s">
-        <v>5469</v>
+        <v>5479</v>
       </c>
       <c r="F1636" t="s">
         <v>17</v>
@@ -56642,13 +56633,13 @@
         <v>7</v>
       </c>
       <c r="B1637" t="s">
-        <v>5477</v>
+        <v>5480</v>
       </c>
       <c r="D1637" t="s">
-        <v>5478</v>
+        <v>5481</v>
       </c>
       <c r="E1637" t="s">
-        <v>5479</v>
+        <v>5482</v>
       </c>
       <c r="F1637" t="s">
         <v>17</v>
@@ -56662,19 +56653,19 @@
         <v>7</v>
       </c>
       <c r="B1638" t="s">
-        <v>5480</v>
+        <v>6561</v>
       </c>
       <c r="D1638" t="s">
-        <v>5481</v>
+        <v>6298</v>
       </c>
       <c r="E1638" t="s">
-        <v>5482</v>
+        <v>6299</v>
       </c>
       <c r="F1638" t="s">
         <v>17</v>
       </c>
       <c r="G1638" t="s">
-        <v>6257</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="1639" spans="1:7" x14ac:dyDescent="0.25">
@@ -56682,19 +56673,19 @@
         <v>7</v>
       </c>
       <c r="B1639" t="s">
-        <v>6561</v>
+        <v>6301</v>
       </c>
       <c r="D1639" t="s">
-        <v>6298</v>
+        <v>6302</v>
       </c>
       <c r="E1639" t="s">
-        <v>6299</v>
+        <v>6303</v>
       </c>
       <c r="F1639" t="s">
         <v>17</v>
       </c>
       <c r="G1639" t="s">
-        <v>6300</v>
+        <v>6257</v>
       </c>
     </row>
     <row r="1640" spans="1:7" x14ac:dyDescent="0.25">
@@ -56702,19 +56693,19 @@
         <v>7</v>
       </c>
       <c r="B1640" t="s">
-        <v>6301</v>
+        <v>5486</v>
       </c>
       <c r="D1640" t="s">
-        <v>6302</v>
+        <v>5487</v>
       </c>
       <c r="E1640" t="s">
-        <v>6303</v>
+        <v>5488</v>
       </c>
       <c r="F1640" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G1640" t="s">
-        <v>6257</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1641" spans="1:7" x14ac:dyDescent="0.25">
@@ -56722,13 +56713,16 @@
         <v>7</v>
       </c>
       <c r="B1641" t="s">
-        <v>5486</v>
+        <v>5489</v>
+      </c>
+      <c r="C1641" t="s">
+        <v>5490</v>
       </c>
       <c r="D1641" t="s">
-        <v>5487</v>
+        <v>5491</v>
       </c>
       <c r="E1641" t="s">
-        <v>5488</v>
+        <v>5492</v>
       </c>
       <c r="F1641" t="s">
         <v>12</v>
@@ -56742,16 +56736,13 @@
         <v>7</v>
       </c>
       <c r="B1642" t="s">
-        <v>5489</v>
-      </c>
-      <c r="C1642" t="s">
-        <v>5490</v>
+        <v>5493</v>
       </c>
       <c r="D1642" t="s">
-        <v>5491</v>
+        <v>5494</v>
       </c>
       <c r="E1642" t="s">
-        <v>5492</v>
+        <v>5495</v>
       </c>
       <c r="F1642" t="s">
         <v>12</v>
@@ -56765,13 +56756,16 @@
         <v>7</v>
       </c>
       <c r="B1643" t="s">
-        <v>5493</v>
+        <v>5496</v>
+      </c>
+      <c r="C1643" t="s">
+        <v>5497</v>
       </c>
       <c r="D1643" t="s">
-        <v>5494</v>
+        <v>5498</v>
       </c>
       <c r="E1643" t="s">
-        <v>5495</v>
+        <v>5499</v>
       </c>
       <c r="F1643" t="s">
         <v>12</v>
@@ -56785,16 +56779,16 @@
         <v>7</v>
       </c>
       <c r="B1644" t="s">
-        <v>5496</v>
+        <v>5500</v>
       </c>
       <c r="C1644" t="s">
-        <v>5497</v>
+        <v>5501</v>
       </c>
       <c r="D1644" t="s">
-        <v>5498</v>
+        <v>5502</v>
       </c>
       <c r="E1644" t="s">
-        <v>5499</v>
+        <v>5503</v>
       </c>
       <c r="F1644" t="s">
         <v>12</v>
@@ -56808,22 +56802,22 @@
         <v>7</v>
       </c>
       <c r="B1645" t="s">
-        <v>5500</v>
+        <v>5504</v>
       </c>
       <c r="C1645" t="s">
-        <v>5501</v>
+        <v>5505</v>
       </c>
       <c r="D1645" t="s">
-        <v>5502</v>
+        <v>5506</v>
       </c>
       <c r="E1645" t="s">
-        <v>5503</v>
+        <v>5507</v>
       </c>
       <c r="F1645" t="s">
         <v>12</v>
       </c>
       <c r="G1645" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1646" spans="1:7" x14ac:dyDescent="0.25">
@@ -56831,22 +56825,22 @@
         <v>7</v>
       </c>
       <c r="B1646" t="s">
-        <v>5504</v>
+        <v>5508</v>
       </c>
       <c r="C1646" t="s">
-        <v>5505</v>
+        <v>5509</v>
       </c>
       <c r="D1646" t="s">
-        <v>5506</v>
+        <v>5510</v>
       </c>
       <c r="E1646" t="s">
-        <v>5507</v>
+        <v>5511</v>
       </c>
       <c r="F1646" t="s">
         <v>12</v>
       </c>
       <c r="G1646" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1647" spans="1:7" x14ac:dyDescent="0.25">
@@ -56854,16 +56848,16 @@
         <v>7</v>
       </c>
       <c r="B1647" t="s">
-        <v>5508</v>
+        <v>5512</v>
       </c>
       <c r="C1647" t="s">
-        <v>5509</v>
+        <v>5513</v>
       </c>
       <c r="D1647" t="s">
-        <v>5510</v>
+        <v>5514</v>
       </c>
       <c r="E1647" t="s">
-        <v>5511</v>
+        <v>5515</v>
       </c>
       <c r="F1647" t="s">
         <v>12</v>
@@ -56877,16 +56871,13 @@
         <v>7</v>
       </c>
       <c r="B1648" t="s">
-        <v>5512</v>
-      </c>
-      <c r="C1648" t="s">
-        <v>5513</v>
+        <v>5516</v>
       </c>
       <c r="D1648" t="s">
-        <v>5514</v>
+        <v>5517</v>
       </c>
       <c r="E1648" t="s">
-        <v>5515</v>
+        <v>5518</v>
       </c>
       <c r="F1648" t="s">
         <v>12</v>
@@ -56900,19 +56891,19 @@
         <v>7</v>
       </c>
       <c r="B1649" t="s">
-        <v>5516</v>
+        <v>6311</v>
       </c>
       <c r="D1649" t="s">
-        <v>5517</v>
+        <v>6312</v>
       </c>
       <c r="E1649" t="s">
-        <v>5518</v>
+        <v>6313</v>
       </c>
       <c r="F1649" t="s">
         <v>12</v>
       </c>
       <c r="G1649" t="s">
-        <v>13</v>
+        <v>6285</v>
       </c>
     </row>
     <row r="1650" spans="1:7" x14ac:dyDescent="0.25">
@@ -56920,19 +56911,22 @@
         <v>7</v>
       </c>
       <c r="B1650" t="s">
-        <v>6311</v>
+        <v>5519</v>
+      </c>
+      <c r="C1650" t="s">
+        <v>5520</v>
       </c>
       <c r="D1650" t="s">
-        <v>6312</v>
+        <v>5521</v>
       </c>
       <c r="E1650" t="s">
-        <v>6313</v>
+        <v>5522</v>
       </c>
       <c r="F1650" t="s">
         <v>12</v>
       </c>
       <c r="G1650" t="s">
-        <v>6285</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1651" spans="1:7" x14ac:dyDescent="0.25">
@@ -56940,16 +56934,16 @@
         <v>7</v>
       </c>
       <c r="B1651" t="s">
-        <v>5519</v>
+        <v>5523</v>
       </c>
       <c r="C1651" t="s">
-        <v>5520</v>
+        <v>5524</v>
       </c>
       <c r="D1651" t="s">
-        <v>5521</v>
+        <v>5525</v>
       </c>
       <c r="E1651" t="s">
-        <v>5522</v>
+        <v>5526</v>
       </c>
       <c r="F1651" t="s">
         <v>12</v>
@@ -56963,16 +56957,16 @@
         <v>7</v>
       </c>
       <c r="B1652" t="s">
-        <v>5523</v>
+        <v>5527</v>
       </c>
       <c r="C1652" t="s">
-        <v>5524</v>
+        <v>5528</v>
       </c>
       <c r="D1652" t="s">
-        <v>5525</v>
+        <v>5529</v>
       </c>
       <c r="E1652" t="s">
-        <v>5526</v>
+        <v>5530</v>
       </c>
       <c r="F1652" t="s">
         <v>12</v>
@@ -56986,16 +56980,13 @@
         <v>7</v>
       </c>
       <c r="B1653" t="s">
-        <v>5527</v>
-      </c>
-      <c r="C1653" t="s">
-        <v>5528</v>
+        <v>5531</v>
       </c>
       <c r="D1653" t="s">
-        <v>5529</v>
+        <v>5532</v>
       </c>
       <c r="E1653" t="s">
-        <v>5530</v>
+        <v>5533</v>
       </c>
       <c r="F1653" t="s">
         <v>12</v>
@@ -57009,13 +57000,16 @@
         <v>7</v>
       </c>
       <c r="B1654" t="s">
-        <v>5531</v>
+        <v>5534</v>
+      </c>
+      <c r="C1654" t="s">
+        <v>5535</v>
       </c>
       <c r="D1654" t="s">
-        <v>5532</v>
+        <v>5536</v>
       </c>
       <c r="E1654" t="s">
-        <v>5533</v>
+        <v>5537</v>
       </c>
       <c r="F1654" t="s">
         <v>12</v>
@@ -57029,16 +57023,13 @@
         <v>7</v>
       </c>
       <c r="B1655" t="s">
-        <v>5534</v>
-      </c>
-      <c r="C1655" t="s">
-        <v>5535</v>
+        <v>5538</v>
       </c>
       <c r="D1655" t="s">
-        <v>5536</v>
+        <v>5539</v>
       </c>
       <c r="E1655" t="s">
-        <v>5537</v>
+        <v>5540</v>
       </c>
       <c r="F1655" t="s">
         <v>12</v>
@@ -57052,13 +57043,16 @@
         <v>7</v>
       </c>
       <c r="B1656" t="s">
-        <v>5538</v>
+        <v>5541</v>
+      </c>
+      <c r="C1656" t="s">
+        <v>5542</v>
       </c>
       <c r="D1656" t="s">
-        <v>5539</v>
+        <v>5543</v>
       </c>
       <c r="E1656" t="s">
-        <v>5540</v>
+        <v>5544</v>
       </c>
       <c r="F1656" t="s">
         <v>12</v>
@@ -57072,16 +57066,16 @@
         <v>7</v>
       </c>
       <c r="B1657" t="s">
-        <v>5541</v>
+        <v>5980</v>
       </c>
       <c r="C1657" t="s">
-        <v>5542</v>
+        <v>5981</v>
       </c>
       <c r="D1657" t="s">
-        <v>5543</v>
+        <v>6562</v>
       </c>
       <c r="E1657" t="s">
-        <v>5544</v>
+        <v>5982</v>
       </c>
       <c r="F1657" t="s">
         <v>12</v>
@@ -57095,16 +57089,16 @@
         <v>7</v>
       </c>
       <c r="B1658" t="s">
-        <v>5980</v>
+        <v>5545</v>
       </c>
       <c r="C1658" t="s">
-        <v>5981</v>
+        <v>5546</v>
       </c>
       <c r="D1658" t="s">
-        <v>6562</v>
+        <v>5547</v>
       </c>
       <c r="E1658" t="s">
-        <v>5982</v>
+        <v>5548</v>
       </c>
       <c r="F1658" t="s">
         <v>12</v>
@@ -57118,22 +57112,19 @@
         <v>7</v>
       </c>
       <c r="B1659" t="s">
-        <v>5545</v>
-      </c>
-      <c r="C1659" t="s">
-        <v>5546</v>
+        <v>5483</v>
       </c>
       <c r="D1659" t="s">
-        <v>5547</v>
+        <v>5484</v>
       </c>
       <c r="E1659" t="s">
-        <v>5548</v>
+        <v>5485</v>
       </c>
       <c r="F1659" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G1659" t="s">
-        <v>13</v>
+        <v>6257</v>
       </c>
     </row>
     <row r="1660" spans="1:7" x14ac:dyDescent="0.25">
@@ -57141,19 +57132,19 @@
         <v>7</v>
       </c>
       <c r="B1660" t="s">
-        <v>5483</v>
+        <v>5549</v>
       </c>
       <c r="D1660" t="s">
-        <v>5484</v>
+        <v>5550</v>
       </c>
       <c r="E1660" t="s">
-        <v>5485</v>
+        <v>5551</v>
       </c>
       <c r="F1660" t="s">
         <v>17</v>
       </c>
       <c r="G1660" t="s">
-        <v>6257</v>
+        <v>6505</v>
       </c>
     </row>
     <row r="1661" spans="1:7" x14ac:dyDescent="0.25">
@@ -57161,19 +57152,22 @@
         <v>7</v>
       </c>
       <c r="B1661" t="s">
-        <v>5549</v>
+        <v>5555</v>
+      </c>
+      <c r="C1661" t="s">
+        <v>5556</v>
       </c>
       <c r="D1661" t="s">
-        <v>5550</v>
+        <v>5557</v>
       </c>
       <c r="E1661" t="s">
-        <v>5551</v>
+        <v>5558</v>
       </c>
       <c r="F1661" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G1661" t="s">
-        <v>6505</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1662" spans="1:7" x14ac:dyDescent="0.25">
@@ -57181,16 +57175,16 @@
         <v>7</v>
       </c>
       <c r="B1662" t="s">
-        <v>5555</v>
+        <v>5559</v>
       </c>
       <c r="C1662" t="s">
-        <v>5556</v>
+        <v>5560</v>
       </c>
       <c r="D1662" t="s">
-        <v>5557</v>
+        <v>5561</v>
       </c>
       <c r="E1662" t="s">
-        <v>5558</v>
+        <v>5562</v>
       </c>
       <c r="F1662" t="s">
         <v>12</v>
@@ -57204,16 +57198,13 @@
         <v>7</v>
       </c>
       <c r="B1663" t="s">
-        <v>5559</v>
-      </c>
-      <c r="C1663" t="s">
-        <v>5560</v>
+        <v>5563</v>
       </c>
       <c r="D1663" t="s">
-        <v>5561</v>
+        <v>5564</v>
       </c>
       <c r="E1663" t="s">
-        <v>5562</v>
+        <v>5565</v>
       </c>
       <c r="F1663" t="s">
         <v>12</v>
@@ -57227,13 +57218,16 @@
         <v>7</v>
       </c>
       <c r="B1664" t="s">
-        <v>5563</v>
+        <v>5566</v>
+      </c>
+      <c r="C1664" t="s">
+        <v>5567</v>
       </c>
       <c r="D1664" t="s">
-        <v>5564</v>
+        <v>5568</v>
       </c>
       <c r="E1664" t="s">
-        <v>5565</v>
+        <v>5569</v>
       </c>
       <c r="F1664" t="s">
         <v>12</v>
@@ -57247,16 +57241,16 @@
         <v>7</v>
       </c>
       <c r="B1665" t="s">
-        <v>5566</v>
+        <v>5570</v>
       </c>
       <c r="C1665" t="s">
-        <v>5567</v>
+        <v>5571</v>
       </c>
       <c r="D1665" t="s">
-        <v>5568</v>
+        <v>5572</v>
       </c>
       <c r="E1665" t="s">
-        <v>5569</v>
+        <v>5573</v>
       </c>
       <c r="F1665" t="s">
         <v>12</v>
@@ -57270,16 +57264,16 @@
         <v>7</v>
       </c>
       <c r="B1666" t="s">
-        <v>5570</v>
+        <v>5574</v>
       </c>
       <c r="C1666" t="s">
-        <v>5571</v>
+        <v>5575</v>
       </c>
       <c r="D1666" t="s">
-        <v>5572</v>
+        <v>5576</v>
       </c>
       <c r="E1666" t="s">
-        <v>5573</v>
+        <v>5577</v>
       </c>
       <c r="F1666" t="s">
         <v>12</v>
@@ -57293,16 +57287,16 @@
         <v>7</v>
       </c>
       <c r="B1667" t="s">
-        <v>5574</v>
+        <v>5578</v>
       </c>
       <c r="C1667" t="s">
-        <v>5575</v>
+        <v>5579</v>
       </c>
       <c r="D1667" t="s">
-        <v>5576</v>
+        <v>5580</v>
       </c>
       <c r="E1667" t="s">
-        <v>5577</v>
+        <v>5581</v>
       </c>
       <c r="F1667" t="s">
         <v>12</v>
@@ -57316,16 +57310,16 @@
         <v>7</v>
       </c>
       <c r="B1668" t="s">
-        <v>5578</v>
+        <v>5582</v>
       </c>
       <c r="C1668" t="s">
-        <v>5579</v>
+        <v>5583</v>
       </c>
       <c r="D1668" t="s">
-        <v>5580</v>
+        <v>5584</v>
       </c>
       <c r="E1668" t="s">
-        <v>5581</v>
+        <v>5585</v>
       </c>
       <c r="F1668" t="s">
         <v>12</v>
@@ -57339,22 +57333,19 @@
         <v>7</v>
       </c>
       <c r="B1669" t="s">
-        <v>5582</v>
-      </c>
-      <c r="C1669" t="s">
-        <v>5583</v>
+        <v>5552</v>
       </c>
       <c r="D1669" t="s">
-        <v>5584</v>
+        <v>5553</v>
       </c>
       <c r="E1669" t="s">
-        <v>5585</v>
+        <v>5554</v>
       </c>
       <c r="F1669" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G1669" t="s">
-        <v>13</v>
+        <v>6257</v>
       </c>
     </row>
     <row r="1670" spans="1:7" x14ac:dyDescent="0.25">
@@ -57362,19 +57353,22 @@
         <v>7</v>
       </c>
       <c r="B1670" t="s">
-        <v>5552</v>
+        <v>5588</v>
+      </c>
+      <c r="C1670" t="s">
+        <v>5589</v>
       </c>
       <c r="D1670" t="s">
-        <v>5553</v>
+        <v>5590</v>
       </c>
       <c r="E1670" t="s">
-        <v>5554</v>
+        <v>5591</v>
       </c>
       <c r="F1670" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G1670" t="s">
-        <v>6257</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1671" spans="1:7" x14ac:dyDescent="0.25">
@@ -57382,16 +57376,16 @@
         <v>7</v>
       </c>
       <c r="B1671" t="s">
-        <v>5588</v>
+        <v>5592</v>
       </c>
       <c r="C1671" t="s">
-        <v>5589</v>
+        <v>5593</v>
       </c>
       <c r="D1671" t="s">
-        <v>5590</v>
+        <v>5594</v>
       </c>
       <c r="E1671" t="s">
-        <v>5591</v>
+        <v>5595</v>
       </c>
       <c r="F1671" t="s">
         <v>12</v>
@@ -57405,16 +57399,16 @@
         <v>7</v>
       </c>
       <c r="B1672" t="s">
-        <v>5592</v>
+        <v>5596</v>
       </c>
       <c r="C1672" t="s">
-        <v>5593</v>
+        <v>5597</v>
       </c>
       <c r="D1672" t="s">
-        <v>5594</v>
+        <v>5598</v>
       </c>
       <c r="E1672" t="s">
-        <v>5595</v>
+        <v>5599</v>
       </c>
       <c r="F1672" t="s">
         <v>12</v>
@@ -57428,16 +57422,16 @@
         <v>7</v>
       </c>
       <c r="B1673" t="s">
-        <v>5596</v>
+        <v>5600</v>
       </c>
       <c r="C1673" t="s">
-        <v>5597</v>
+        <v>5601</v>
       </c>
       <c r="D1673" t="s">
-        <v>5598</v>
+        <v>5602</v>
       </c>
       <c r="E1673" t="s">
-        <v>5599</v>
+        <v>5603</v>
       </c>
       <c r="F1673" t="s">
         <v>12</v>
@@ -57451,16 +57445,16 @@
         <v>7</v>
       </c>
       <c r="B1674" t="s">
-        <v>5600</v>
+        <v>5604</v>
       </c>
       <c r="C1674" t="s">
-        <v>5601</v>
+        <v>5605</v>
       </c>
       <c r="D1674" t="s">
-        <v>5602</v>
+        <v>5606</v>
       </c>
       <c r="E1674" t="s">
-        <v>5603</v>
+        <v>5607</v>
       </c>
       <c r="F1674" t="s">
         <v>12</v>
@@ -57471,25 +57465,22 @@
     </row>
     <row r="1675" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1675" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B1675" t="s">
-        <v>5604</v>
-      </c>
-      <c r="C1675" t="s">
-        <v>5605</v>
+        <v>5586</v>
       </c>
       <c r="D1675" t="s">
-        <v>5606</v>
+        <v>5587</v>
       </c>
       <c r="E1675" t="s">
-        <v>5607</v>
+        <v>6781</v>
       </c>
       <c r="F1675" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G1675" t="s">
-        <v>13</v>
+        <v>6257</v>
       </c>
     </row>
     <row r="1676" spans="1:7" x14ac:dyDescent="0.25">
@@ -57497,13 +57488,13 @@
         <v>14</v>
       </c>
       <c r="B1676" t="s">
-        <v>5586</v>
+        <v>5608</v>
       </c>
       <c r="D1676" t="s">
-        <v>5587</v>
+        <v>5609</v>
       </c>
       <c r="E1676" t="s">
-        <v>6781</v>
+        <v>6782</v>
       </c>
       <c r="F1676" t="s">
         <v>17</v>
@@ -57514,22 +57505,25 @@
     </row>
     <row r="1677" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1677" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B1677" t="s">
-        <v>5608</v>
+        <v>5613</v>
+      </c>
+      <c r="C1677" t="s">
+        <v>5614</v>
       </c>
       <c r="D1677" t="s">
-        <v>5609</v>
+        <v>5615</v>
       </c>
       <c r="E1677" t="s">
-        <v>6782</v>
+        <v>5616</v>
       </c>
       <c r="F1677" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G1677" t="s">
-        <v>6257</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1678" spans="1:7" x14ac:dyDescent="0.25">
@@ -57537,22 +57531,19 @@
         <v>7</v>
       </c>
       <c r="B1678" t="s">
-        <v>5613</v>
-      </c>
-      <c r="C1678" t="s">
-        <v>5614</v>
+        <v>5610</v>
       </c>
       <c r="D1678" t="s">
-        <v>5615</v>
+        <v>5611</v>
       </c>
       <c r="E1678" t="s">
-        <v>5616</v>
+        <v>5612</v>
       </c>
       <c r="F1678" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G1678" t="s">
-        <v>13</v>
+        <v>6791</v>
       </c>
     </row>
     <row r="1679" spans="1:7" x14ac:dyDescent="0.25">
@@ -57560,19 +57551,22 @@
         <v>7</v>
       </c>
       <c r="B1679" t="s">
-        <v>5610</v>
+        <v>5619</v>
+      </c>
+      <c r="C1679" t="s">
+        <v>5620</v>
       </c>
       <c r="D1679" t="s">
-        <v>5611</v>
+        <v>5621</v>
       </c>
       <c r="E1679" t="s">
-        <v>5612</v>
+        <v>5622</v>
       </c>
       <c r="F1679" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G1679" t="s">
-        <v>6791</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1680" spans="1:7" x14ac:dyDescent="0.25">
@@ -57580,16 +57574,16 @@
         <v>7</v>
       </c>
       <c r="B1680" t="s">
-        <v>5619</v>
+        <v>5623</v>
       </c>
       <c r="C1680" t="s">
-        <v>5620</v>
+        <v>5624</v>
       </c>
       <c r="D1680" t="s">
-        <v>5621</v>
+        <v>5625</v>
       </c>
       <c r="E1680" t="s">
-        <v>5622</v>
+        <v>5626</v>
       </c>
       <c r="F1680" t="s">
         <v>12</v>
@@ -57603,16 +57597,13 @@
         <v>7</v>
       </c>
       <c r="B1681" t="s">
-        <v>5623</v>
-      </c>
-      <c r="C1681" t="s">
-        <v>5624</v>
+        <v>5627</v>
       </c>
       <c r="D1681" t="s">
-        <v>5625</v>
+        <v>5628</v>
       </c>
       <c r="E1681" t="s">
-        <v>5626</v>
+        <v>5629</v>
       </c>
       <c r="F1681" t="s">
         <v>12</v>
@@ -57626,13 +57617,16 @@
         <v>7</v>
       </c>
       <c r="B1682" t="s">
-        <v>5627</v>
+        <v>5630</v>
+      </c>
+      <c r="C1682" t="s">
+        <v>5631</v>
       </c>
       <c r="D1682" t="s">
-        <v>5628</v>
+        <v>5632</v>
       </c>
       <c r="E1682" t="s">
-        <v>5629</v>
+        <v>5633</v>
       </c>
       <c r="F1682" t="s">
         <v>12</v>
@@ -57646,16 +57640,16 @@
         <v>7</v>
       </c>
       <c r="B1683" t="s">
-        <v>5630</v>
+        <v>5634</v>
       </c>
       <c r="C1683" t="s">
-        <v>5631</v>
+        <v>5635</v>
       </c>
       <c r="D1683" t="s">
-        <v>5632</v>
+        <v>5636</v>
       </c>
       <c r="E1683" t="s">
-        <v>5633</v>
+        <v>5637</v>
       </c>
       <c r="F1683" t="s">
         <v>12</v>
@@ -57669,16 +57663,16 @@
         <v>7</v>
       </c>
       <c r="B1684" t="s">
-        <v>5634</v>
+        <v>5638</v>
       </c>
       <c r="C1684" t="s">
-        <v>5635</v>
+        <v>5639</v>
       </c>
       <c r="D1684" t="s">
-        <v>5636</v>
+        <v>5640</v>
       </c>
       <c r="E1684" t="s">
-        <v>5637</v>
+        <v>5641</v>
       </c>
       <c r="F1684" t="s">
         <v>12</v>
@@ -57692,16 +57686,16 @@
         <v>7</v>
       </c>
       <c r="B1685" t="s">
-        <v>5638</v>
+        <v>5642</v>
       </c>
       <c r="C1685" t="s">
-        <v>5639</v>
+        <v>5643</v>
       </c>
       <c r="D1685" t="s">
-        <v>5640</v>
+        <v>5644</v>
       </c>
       <c r="E1685" t="s">
-        <v>5641</v>
+        <v>5645</v>
       </c>
       <c r="F1685" t="s">
         <v>12</v>
@@ -57715,16 +57709,16 @@
         <v>7</v>
       </c>
       <c r="B1686" t="s">
-        <v>5642</v>
+        <v>5646</v>
       </c>
       <c r="C1686" t="s">
-        <v>5643</v>
+        <v>5647</v>
       </c>
       <c r="D1686" t="s">
-        <v>5644</v>
+        <v>5648</v>
       </c>
       <c r="E1686" t="s">
-        <v>5645</v>
+        <v>5649</v>
       </c>
       <c r="F1686" t="s">
         <v>12</v>
@@ -57735,45 +57729,45 @@
     </row>
     <row r="1687" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1687" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B1687" t="s">
-        <v>5646</v>
-      </c>
-      <c r="C1687" t="s">
-        <v>5647</v>
+        <v>5617</v>
       </c>
       <c r="D1687" t="s">
-        <v>5648</v>
+        <v>5618</v>
       </c>
       <c r="E1687" t="s">
-        <v>5649</v>
+        <v>6783</v>
       </c>
       <c r="F1687" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G1687" t="s">
-        <v>13</v>
+        <v>6257</v>
       </c>
     </row>
     <row r="1688" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1688" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B1688" t="s">
-        <v>5617</v>
+        <v>5653</v>
+      </c>
+      <c r="C1688" t="s">
+        <v>5654</v>
       </c>
       <c r="D1688" t="s">
-        <v>5618</v>
+        <v>5655</v>
       </c>
       <c r="E1688" t="s">
-        <v>6783</v>
+        <v>5656</v>
       </c>
       <c r="F1688" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G1688" t="s">
-        <v>6257</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1689" spans="1:7" x14ac:dyDescent="0.25">
@@ -57781,22 +57775,19 @@
         <v>7</v>
       </c>
       <c r="B1689" t="s">
-        <v>5653</v>
-      </c>
-      <c r="C1689" t="s">
-        <v>5654</v>
+        <v>5650</v>
       </c>
       <c r="D1689" t="s">
-        <v>5655</v>
+        <v>5651</v>
       </c>
       <c r="E1689" t="s">
-        <v>5656</v>
+        <v>5652</v>
       </c>
       <c r="F1689" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G1689" t="s">
-        <v>13</v>
+        <v>6257</v>
       </c>
     </row>
     <row r="1690" spans="1:7" x14ac:dyDescent="0.25">
@@ -57804,19 +57795,22 @@
         <v>7</v>
       </c>
       <c r="B1690" t="s">
-        <v>5650</v>
+        <v>5660</v>
+      </c>
+      <c r="C1690" t="s">
+        <v>5661</v>
       </c>
       <c r="D1690" t="s">
-        <v>5651</v>
+        <v>5662</v>
       </c>
       <c r="E1690" t="s">
-        <v>5652</v>
+        <v>5663</v>
       </c>
       <c r="F1690" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G1690" t="s">
-        <v>6257</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1691" spans="1:7" x14ac:dyDescent="0.25">
@@ -57824,16 +57818,16 @@
         <v>7</v>
       </c>
       <c r="B1691" t="s">
-        <v>5660</v>
+        <v>5664</v>
       </c>
       <c r="C1691" t="s">
-        <v>5661</v>
+        <v>5665</v>
       </c>
       <c r="D1691" t="s">
-        <v>5662</v>
+        <v>5666</v>
       </c>
       <c r="E1691" t="s">
-        <v>5663</v>
+        <v>5667</v>
       </c>
       <c r="F1691" t="s">
         <v>12</v>
@@ -57847,16 +57841,16 @@
         <v>7</v>
       </c>
       <c r="B1692" t="s">
-        <v>5664</v>
+        <v>5668</v>
       </c>
       <c r="C1692" t="s">
-        <v>5665</v>
+        <v>5669</v>
       </c>
       <c r="D1692" t="s">
-        <v>5666</v>
+        <v>5670</v>
       </c>
       <c r="E1692" t="s">
-        <v>5667</v>
+        <v>5671</v>
       </c>
       <c r="F1692" t="s">
         <v>12</v>
@@ -57870,16 +57864,16 @@
         <v>7</v>
       </c>
       <c r="B1693" t="s">
-        <v>5668</v>
+        <v>5672</v>
       </c>
       <c r="C1693" t="s">
-        <v>5669</v>
+        <v>5673</v>
       </c>
       <c r="D1693" t="s">
-        <v>5670</v>
+        <v>5674</v>
       </c>
       <c r="E1693" t="s">
-        <v>5671</v>
+        <v>5675</v>
       </c>
       <c r="F1693" t="s">
         <v>12</v>
@@ -57893,16 +57887,16 @@
         <v>7</v>
       </c>
       <c r="B1694" t="s">
-        <v>5672</v>
+        <v>5676</v>
       </c>
       <c r="C1694" t="s">
-        <v>5673</v>
+        <v>5677</v>
       </c>
       <c r="D1694" t="s">
-        <v>5674</v>
+        <v>5678</v>
       </c>
       <c r="E1694" t="s">
-        <v>5675</v>
+        <v>5679</v>
       </c>
       <c r="F1694" t="s">
         <v>12</v>
@@ -57916,16 +57910,16 @@
         <v>7</v>
       </c>
       <c r="B1695" t="s">
-        <v>5676</v>
+        <v>5680</v>
       </c>
       <c r="C1695" t="s">
-        <v>5677</v>
+        <v>5681</v>
       </c>
       <c r="D1695" t="s">
-        <v>5678</v>
+        <v>5682</v>
       </c>
       <c r="E1695" t="s">
-        <v>5679</v>
+        <v>5683</v>
       </c>
       <c r="F1695" t="s">
         <v>12</v>
@@ -57939,16 +57933,16 @@
         <v>7</v>
       </c>
       <c r="B1696" t="s">
-        <v>5680</v>
+        <v>5684</v>
       </c>
       <c r="C1696" t="s">
-        <v>5681</v>
+        <v>5685</v>
       </c>
       <c r="D1696" t="s">
-        <v>5682</v>
+        <v>5686</v>
       </c>
       <c r="E1696" t="s">
-        <v>5683</v>
+        <v>5687</v>
       </c>
       <c r="F1696" t="s">
         <v>12</v>
@@ -57962,16 +57956,16 @@
         <v>7</v>
       </c>
       <c r="B1697" t="s">
-        <v>5684</v>
+        <v>5688</v>
       </c>
       <c r="C1697" t="s">
-        <v>5685</v>
+        <v>5689</v>
       </c>
       <c r="D1697" t="s">
-        <v>5686</v>
+        <v>6563</v>
       </c>
       <c r="E1697" t="s">
-        <v>5687</v>
+        <v>5690</v>
       </c>
       <c r="F1697" t="s">
         <v>12</v>
@@ -57985,16 +57979,16 @@
         <v>7</v>
       </c>
       <c r="B1698" t="s">
-        <v>5688</v>
+        <v>5691</v>
       </c>
       <c r="C1698" t="s">
-        <v>5689</v>
+        <v>5692</v>
       </c>
       <c r="D1698" t="s">
-        <v>6563</v>
+        <v>5693</v>
       </c>
       <c r="E1698" t="s">
-        <v>5690</v>
+        <v>5694</v>
       </c>
       <c r="F1698" t="s">
         <v>12</v>
@@ -58008,16 +58002,16 @@
         <v>7</v>
       </c>
       <c r="B1699" t="s">
-        <v>5691</v>
+        <v>5695</v>
       </c>
       <c r="C1699" t="s">
-        <v>5692</v>
+        <v>5696</v>
       </c>
       <c r="D1699" t="s">
-        <v>5693</v>
+        <v>5697</v>
       </c>
       <c r="E1699" t="s">
-        <v>5694</v>
+        <v>5698</v>
       </c>
       <c r="F1699" t="s">
         <v>12</v>
@@ -58031,16 +58025,16 @@
         <v>7</v>
       </c>
       <c r="B1700" t="s">
-        <v>5695</v>
+        <v>5699</v>
       </c>
       <c r="C1700" t="s">
-        <v>5696</v>
+        <v>5700</v>
       </c>
       <c r="D1700" t="s">
-        <v>5697</v>
+        <v>5701</v>
       </c>
       <c r="E1700" t="s">
-        <v>5698</v>
+        <v>5702</v>
       </c>
       <c r="F1700" t="s">
         <v>12</v>
@@ -58054,16 +58048,16 @@
         <v>7</v>
       </c>
       <c r="B1701" t="s">
-        <v>5699</v>
+        <v>5703</v>
       </c>
       <c r="C1701" t="s">
-        <v>5700</v>
+        <v>5704</v>
       </c>
       <c r="D1701" t="s">
-        <v>5701</v>
+        <v>5705</v>
       </c>
       <c r="E1701" t="s">
-        <v>5702</v>
+        <v>5706</v>
       </c>
       <c r="F1701" t="s">
         <v>12</v>
@@ -58077,16 +58071,16 @@
         <v>7</v>
       </c>
       <c r="B1702" t="s">
-        <v>5703</v>
+        <v>5707</v>
       </c>
       <c r="C1702" t="s">
-        <v>5704</v>
+        <v>5708</v>
       </c>
       <c r="D1702" t="s">
-        <v>5705</v>
+        <v>5709</v>
       </c>
       <c r="E1702" t="s">
-        <v>5706</v>
+        <v>5710</v>
       </c>
       <c r="F1702" t="s">
         <v>12</v>
@@ -58100,16 +58094,16 @@
         <v>7</v>
       </c>
       <c r="B1703" t="s">
-        <v>5707</v>
+        <v>5711</v>
       </c>
       <c r="C1703" t="s">
-        <v>5708</v>
+        <v>5712</v>
       </c>
       <c r="D1703" t="s">
-        <v>5709</v>
+        <v>5713</v>
       </c>
       <c r="E1703" t="s">
-        <v>5710</v>
+        <v>5714</v>
       </c>
       <c r="F1703" t="s">
         <v>12</v>
@@ -58123,16 +58117,16 @@
         <v>7</v>
       </c>
       <c r="B1704" t="s">
-        <v>5711</v>
+        <v>5715</v>
       </c>
       <c r="C1704" t="s">
-        <v>5712</v>
+        <v>5716</v>
       </c>
       <c r="D1704" t="s">
-        <v>5713</v>
+        <v>5717</v>
       </c>
       <c r="E1704" t="s">
-        <v>5714</v>
+        <v>5718</v>
       </c>
       <c r="F1704" t="s">
         <v>12</v>
@@ -58146,16 +58140,16 @@
         <v>7</v>
       </c>
       <c r="B1705" t="s">
-        <v>5715</v>
+        <v>5719</v>
       </c>
       <c r="C1705" t="s">
-        <v>5716</v>
+        <v>5720</v>
       </c>
       <c r="D1705" t="s">
-        <v>5717</v>
+        <v>5721</v>
       </c>
       <c r="E1705" t="s">
-        <v>5718</v>
+        <v>5722</v>
       </c>
       <c r="F1705" t="s">
         <v>12</v>
@@ -58169,16 +58163,16 @@
         <v>7</v>
       </c>
       <c r="B1706" t="s">
-        <v>5719</v>
+        <v>5723</v>
       </c>
       <c r="C1706" t="s">
-        <v>5720</v>
+        <v>5724</v>
       </c>
       <c r="D1706" t="s">
-        <v>5721</v>
+        <v>5725</v>
       </c>
       <c r="E1706" t="s">
-        <v>5722</v>
+        <v>5726</v>
       </c>
       <c r="F1706" t="s">
         <v>12</v>
@@ -58192,16 +58186,16 @@
         <v>7</v>
       </c>
       <c r="B1707" t="s">
-        <v>5723</v>
+        <v>5727</v>
       </c>
       <c r="C1707" t="s">
-        <v>5724</v>
+        <v>5728</v>
       </c>
       <c r="D1707" t="s">
-        <v>5725</v>
+        <v>5729</v>
       </c>
       <c r="E1707" t="s">
-        <v>5726</v>
+        <v>5730</v>
       </c>
       <c r="F1707" t="s">
         <v>12</v>
@@ -58215,16 +58209,16 @@
         <v>7</v>
       </c>
       <c r="B1708" t="s">
-        <v>5727</v>
+        <v>5731</v>
       </c>
       <c r="C1708" t="s">
-        <v>5728</v>
+        <v>5732</v>
       </c>
       <c r="D1708" t="s">
-        <v>5729</v>
+        <v>5733</v>
       </c>
       <c r="E1708" t="s">
-        <v>5730</v>
+        <v>5734</v>
       </c>
       <c r="F1708" t="s">
         <v>12</v>
@@ -58238,16 +58232,16 @@
         <v>7</v>
       </c>
       <c r="B1709" t="s">
-        <v>5731</v>
+        <v>5735</v>
       </c>
       <c r="C1709" t="s">
-        <v>5732</v>
+        <v>5736</v>
       </c>
       <c r="D1709" t="s">
-        <v>5733</v>
+        <v>5737</v>
       </c>
       <c r="E1709" t="s">
-        <v>5734</v>
+        <v>5738</v>
       </c>
       <c r="F1709" t="s">
         <v>12</v>
@@ -58261,16 +58255,16 @@
         <v>7</v>
       </c>
       <c r="B1710" t="s">
-        <v>5735</v>
+        <v>5739</v>
       </c>
       <c r="C1710" t="s">
-        <v>5736</v>
+        <v>5740</v>
       </c>
       <c r="D1710" t="s">
-        <v>5737</v>
+        <v>5741</v>
       </c>
       <c r="E1710" t="s">
-        <v>5738</v>
+        <v>5742</v>
       </c>
       <c r="F1710" t="s">
         <v>12</v>
@@ -58284,22 +58278,19 @@
         <v>7</v>
       </c>
       <c r="B1711" t="s">
-        <v>5739</v>
-      </c>
-      <c r="C1711" t="s">
-        <v>5740</v>
+        <v>5657</v>
       </c>
       <c r="D1711" t="s">
-        <v>5741</v>
+        <v>5658</v>
       </c>
       <c r="E1711" t="s">
-        <v>5742</v>
+        <v>5659</v>
       </c>
       <c r="F1711" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G1711" t="s">
-        <v>13</v>
+        <v>6257</v>
       </c>
     </row>
     <row r="1712" spans="1:7" x14ac:dyDescent="0.25">
@@ -58307,62 +58298,65 @@
         <v>7</v>
       </c>
       <c r="B1712" t="s">
-        <v>5657</v>
+        <v>5745</v>
+      </c>
+      <c r="C1712" t="s">
+        <v>5746</v>
       </c>
       <c r="D1712" t="s">
-        <v>5658</v>
+        <v>5747</v>
       </c>
       <c r="E1712" t="s">
-        <v>5659</v>
+        <v>5748</v>
       </c>
       <c r="F1712" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G1712" t="s">
-        <v>6257</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1713" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1713" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B1713" t="s">
-        <v>5745</v>
-      </c>
-      <c r="C1713" t="s">
-        <v>5746</v>
+        <v>5743</v>
       </c>
       <c r="D1713" t="s">
-        <v>5747</v>
+        <v>5744</v>
       </c>
       <c r="E1713" t="s">
-        <v>5748</v>
+        <v>6784</v>
       </c>
       <c r="F1713" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G1713" t="s">
-        <v>13</v>
+        <v>6257</v>
       </c>
     </row>
     <row r="1714" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1714" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B1714" t="s">
-        <v>5743</v>
+        <v>5756</v>
+      </c>
+      <c r="C1714" t="s">
+        <v>5757</v>
       </c>
       <c r="D1714" t="s">
-        <v>5744</v>
+        <v>5758</v>
       </c>
       <c r="E1714" t="s">
-        <v>6784</v>
+        <v>5759</v>
       </c>
       <c r="F1714" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G1714" t="s">
-        <v>6257</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1715" spans="1:7" x14ac:dyDescent="0.25">
@@ -58370,16 +58364,16 @@
         <v>7</v>
       </c>
       <c r="B1715" t="s">
-        <v>5756</v>
+        <v>5760</v>
       </c>
       <c r="C1715" t="s">
-        <v>5757</v>
+        <v>5761</v>
       </c>
       <c r="D1715" t="s">
-        <v>5758</v>
+        <v>5762</v>
       </c>
       <c r="E1715" t="s">
-        <v>5759</v>
+        <v>5763</v>
       </c>
       <c r="F1715" t="s">
         <v>12</v>
@@ -58393,16 +58387,16 @@
         <v>7</v>
       </c>
       <c r="B1716" t="s">
-        <v>5760</v>
+        <v>5764</v>
       </c>
       <c r="C1716" t="s">
-        <v>5761</v>
+        <v>5765</v>
       </c>
       <c r="D1716" t="s">
-        <v>5762</v>
+        <v>5766</v>
       </c>
       <c r="E1716" t="s">
-        <v>5763</v>
+        <v>5767</v>
       </c>
       <c r="F1716" t="s">
         <v>12</v>
@@ -58416,16 +58410,16 @@
         <v>7</v>
       </c>
       <c r="B1717" t="s">
-        <v>5764</v>
+        <v>5768</v>
       </c>
       <c r="C1717" t="s">
-        <v>5765</v>
+        <v>5769</v>
       </c>
       <c r="D1717" t="s">
-        <v>5766</v>
+        <v>5770</v>
       </c>
       <c r="E1717" t="s">
-        <v>5767</v>
+        <v>5771</v>
       </c>
       <c r="F1717" t="s">
         <v>12</v>
@@ -58439,22 +58433,19 @@
         <v>7</v>
       </c>
       <c r="B1718" t="s">
-        <v>5768</v>
-      </c>
-      <c r="C1718" t="s">
-        <v>5769</v>
+        <v>5749</v>
       </c>
       <c r="D1718" t="s">
-        <v>5770</v>
+        <v>5750</v>
       </c>
       <c r="E1718" t="s">
-        <v>5771</v>
+        <v>5751</v>
       </c>
       <c r="F1718" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G1718" t="s">
-        <v>13</v>
+        <v>6257</v>
       </c>
     </row>
     <row r="1719" spans="1:7" x14ac:dyDescent="0.25">
@@ -58462,19 +58453,22 @@
         <v>7</v>
       </c>
       <c r="B1719" t="s">
-        <v>5749</v>
+        <v>5776</v>
+      </c>
+      <c r="C1719" t="s">
+        <v>5777</v>
       </c>
       <c r="D1719" t="s">
-        <v>5750</v>
+        <v>5778</v>
       </c>
       <c r="E1719" t="s">
-        <v>5751</v>
+        <v>5779</v>
       </c>
       <c r="F1719" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G1719" t="s">
-        <v>6257</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1720" spans="1:7" x14ac:dyDescent="0.25">
@@ -58482,22 +58476,22 @@
         <v>7</v>
       </c>
       <c r="B1720" t="s">
-        <v>5776</v>
+        <v>5772</v>
       </c>
       <c r="C1720" t="s">
-        <v>5777</v>
+        <v>5773</v>
       </c>
       <c r="D1720" t="s">
-        <v>5778</v>
+        <v>5774</v>
       </c>
       <c r="E1720" t="s">
-        <v>5779</v>
+        <v>5775</v>
       </c>
       <c r="F1720" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G1720" t="s">
-        <v>13</v>
+        <v>6257</v>
       </c>
     </row>
     <row r="1721" spans="1:7" x14ac:dyDescent="0.25">
@@ -58505,22 +58499,22 @@
         <v>7</v>
       </c>
       <c r="B1721" t="s">
-        <v>5772</v>
+        <v>5783</v>
       </c>
       <c r="C1721" t="s">
-        <v>5773</v>
+        <v>5784</v>
       </c>
       <c r="D1721" t="s">
-        <v>5774</v>
+        <v>5785</v>
       </c>
       <c r="E1721" t="s">
-        <v>5775</v>
+        <v>5786</v>
       </c>
       <c r="F1721" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G1721" t="s">
-        <v>6257</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1722" spans="1:7" x14ac:dyDescent="0.25">
@@ -58528,16 +58522,16 @@
         <v>7</v>
       </c>
       <c r="B1722" t="s">
-        <v>5783</v>
+        <v>1807</v>
       </c>
       <c r="C1722" t="s">
-        <v>5784</v>
+        <v>1808</v>
       </c>
       <c r="D1722" t="s">
-        <v>5785</v>
+        <v>6564</v>
       </c>
       <c r="E1722" t="s">
-        <v>5786</v>
+        <v>1809</v>
       </c>
       <c r="F1722" t="s">
         <v>12</v>
@@ -58551,16 +58545,16 @@
         <v>7</v>
       </c>
       <c r="B1723" t="s">
-        <v>1807</v>
+        <v>5787</v>
       </c>
       <c r="C1723" t="s">
-        <v>1808</v>
+        <v>5788</v>
       </c>
       <c r="D1723" t="s">
-        <v>6564</v>
+        <v>5789</v>
       </c>
       <c r="E1723" t="s">
-        <v>1809</v>
+        <v>5790</v>
       </c>
       <c r="F1723" t="s">
         <v>12</v>
@@ -58574,16 +58568,13 @@
         <v>7</v>
       </c>
       <c r="B1724" t="s">
-        <v>5787</v>
-      </c>
-      <c r="C1724" t="s">
-        <v>5788</v>
+        <v>5791</v>
       </c>
       <c r="D1724" t="s">
-        <v>5789</v>
+        <v>5792</v>
       </c>
       <c r="E1724" t="s">
-        <v>5790</v>
+        <v>5793</v>
       </c>
       <c r="F1724" t="s">
         <v>12</v>
@@ -58597,13 +58588,13 @@
         <v>7</v>
       </c>
       <c r="B1725" t="s">
-        <v>5791</v>
+        <v>5794</v>
       </c>
       <c r="D1725" t="s">
-        <v>5792</v>
+        <v>5795</v>
       </c>
       <c r="E1725" t="s">
-        <v>5793</v>
+        <v>5796</v>
       </c>
       <c r="F1725" t="s">
         <v>12</v>
@@ -58617,13 +58608,16 @@
         <v>7</v>
       </c>
       <c r="B1726" t="s">
-        <v>5794</v>
+        <v>5797</v>
+      </c>
+      <c r="C1726" t="s">
+        <v>5798</v>
       </c>
       <c r="D1726" t="s">
-        <v>5795</v>
+        <v>5799</v>
       </c>
       <c r="E1726" t="s">
-        <v>5796</v>
+        <v>5800</v>
       </c>
       <c r="F1726" t="s">
         <v>12</v>
@@ -58637,16 +58631,16 @@
         <v>7</v>
       </c>
       <c r="B1727" t="s">
-        <v>5797</v>
+        <v>5801</v>
       </c>
       <c r="C1727" t="s">
-        <v>5798</v>
+        <v>5802</v>
       </c>
       <c r="D1727" t="s">
-        <v>5799</v>
+        <v>5803</v>
       </c>
       <c r="E1727" t="s">
-        <v>5800</v>
+        <v>5804</v>
       </c>
       <c r="F1727" t="s">
         <v>12</v>
@@ -58660,16 +58654,16 @@
         <v>7</v>
       </c>
       <c r="B1728" t="s">
-        <v>5801</v>
+        <v>5805</v>
       </c>
       <c r="C1728" t="s">
-        <v>5802</v>
+        <v>5806</v>
       </c>
       <c r="D1728" t="s">
-        <v>5803</v>
+        <v>5807</v>
       </c>
       <c r="E1728" t="s">
-        <v>5804</v>
+        <v>5808</v>
       </c>
       <c r="F1728" t="s">
         <v>12</v>
@@ -58683,16 +58677,16 @@
         <v>7</v>
       </c>
       <c r="B1729" t="s">
-        <v>5805</v>
+        <v>5809</v>
       </c>
       <c r="C1729" t="s">
-        <v>5806</v>
+        <v>5810</v>
       </c>
       <c r="D1729" t="s">
-        <v>5807</v>
+        <v>5811</v>
       </c>
       <c r="E1729" t="s">
-        <v>5808</v>
+        <v>5812</v>
       </c>
       <c r="F1729" t="s">
         <v>12</v>
@@ -58706,16 +58700,16 @@
         <v>7</v>
       </c>
       <c r="B1730" t="s">
-        <v>5809</v>
+        <v>5813</v>
       </c>
       <c r="C1730" t="s">
-        <v>5810</v>
+        <v>5814</v>
       </c>
       <c r="D1730" t="s">
-        <v>5811</v>
+        <v>5815</v>
       </c>
       <c r="E1730" t="s">
-        <v>5812</v>
+        <v>5816</v>
       </c>
       <c r="F1730" t="s">
         <v>12</v>
@@ -58729,16 +58723,16 @@
         <v>7</v>
       </c>
       <c r="B1731" t="s">
-        <v>5813</v>
+        <v>5817</v>
       </c>
       <c r="C1731" t="s">
-        <v>5814</v>
+        <v>5818</v>
       </c>
       <c r="D1731" t="s">
-        <v>5815</v>
+        <v>6565</v>
       </c>
       <c r="E1731" t="s">
-        <v>5816</v>
+        <v>5819</v>
       </c>
       <c r="F1731" t="s">
         <v>12</v>
@@ -58752,16 +58746,16 @@
         <v>7</v>
       </c>
       <c r="B1732" t="s">
-        <v>5817</v>
+        <v>5820</v>
       </c>
       <c r="C1732" t="s">
-        <v>5818</v>
+        <v>5821</v>
       </c>
       <c r="D1732" t="s">
-        <v>6565</v>
+        <v>5822</v>
       </c>
       <c r="E1732" t="s">
-        <v>5819</v>
+        <v>5823</v>
       </c>
       <c r="F1732" t="s">
         <v>12</v>
@@ -58775,16 +58769,16 @@
         <v>7</v>
       </c>
       <c r="B1733" t="s">
-        <v>5820</v>
+        <v>5824</v>
       </c>
       <c r="C1733" t="s">
-        <v>5821</v>
+        <v>5825</v>
       </c>
       <c r="D1733" t="s">
-        <v>5822</v>
+        <v>5826</v>
       </c>
       <c r="E1733" t="s">
-        <v>5823</v>
+        <v>5827</v>
       </c>
       <c r="F1733" t="s">
         <v>12</v>
@@ -58798,16 +58792,16 @@
         <v>7</v>
       </c>
       <c r="B1734" t="s">
-        <v>5824</v>
+        <v>5828</v>
       </c>
       <c r="C1734" t="s">
-        <v>5825</v>
+        <v>5829</v>
       </c>
       <c r="D1734" t="s">
-        <v>5826</v>
+        <v>5830</v>
       </c>
       <c r="E1734" t="s">
-        <v>5827</v>
+        <v>5831</v>
       </c>
       <c r="F1734" t="s">
         <v>12</v>
@@ -58821,22 +58815,19 @@
         <v>7</v>
       </c>
       <c r="B1735" t="s">
-        <v>5828</v>
-      </c>
-      <c r="C1735" t="s">
-        <v>5829</v>
+        <v>5780</v>
       </c>
       <c r="D1735" t="s">
-        <v>5830</v>
+        <v>5781</v>
       </c>
       <c r="E1735" t="s">
-        <v>5831</v>
+        <v>5782</v>
       </c>
       <c r="F1735" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G1735" t="s">
-        <v>13</v>
+        <v>6257</v>
       </c>
     </row>
     <row r="1736" spans="1:7" x14ac:dyDescent="0.25">
@@ -58844,19 +58835,22 @@
         <v>7</v>
       </c>
       <c r="B1736" t="s">
-        <v>5780</v>
+        <v>3390</v>
+      </c>
+      <c r="C1736" t="s">
+        <v>3391</v>
       </c>
       <c r="D1736" t="s">
-        <v>5781</v>
+        <v>6566</v>
       </c>
       <c r="E1736" t="s">
-        <v>5782</v>
+        <v>3392</v>
       </c>
       <c r="F1736" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G1736" t="s">
-        <v>6257</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1737" spans="1:7" x14ac:dyDescent="0.25">
@@ -58864,22 +58858,22 @@
         <v>7</v>
       </c>
       <c r="B1737" t="s">
-        <v>3390</v>
+        <v>5838</v>
       </c>
       <c r="C1737" t="s">
-        <v>3391</v>
+        <v>5839</v>
       </c>
       <c r="D1737" t="s">
-        <v>6566</v>
+        <v>5840</v>
       </c>
       <c r="E1737" t="s">
-        <v>3392</v>
+        <v>5841</v>
       </c>
       <c r="F1737" t="s">
         <v>12</v>
       </c>
       <c r="G1737" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1738" spans="1:7" x14ac:dyDescent="0.25">
@@ -58887,16 +58881,16 @@
         <v>7</v>
       </c>
       <c r="B1738" t="s">
-        <v>5838</v>
+        <v>5842</v>
       </c>
       <c r="C1738" t="s">
-        <v>5839</v>
+        <v>5843</v>
       </c>
       <c r="D1738" t="s">
-        <v>5840</v>
+        <v>5844</v>
       </c>
       <c r="E1738" t="s">
-        <v>5841</v>
+        <v>5845</v>
       </c>
       <c r="F1738" t="s">
         <v>12</v>
@@ -58910,16 +58904,16 @@
         <v>7</v>
       </c>
       <c r="B1739" t="s">
-        <v>5842</v>
+        <v>5846</v>
       </c>
       <c r="C1739" t="s">
-        <v>5843</v>
+        <v>5847</v>
       </c>
       <c r="D1739" t="s">
-        <v>5844</v>
+        <v>5848</v>
       </c>
       <c r="E1739" t="s">
-        <v>5845</v>
+        <v>5849</v>
       </c>
       <c r="F1739" t="s">
         <v>12</v>
@@ -58933,22 +58927,19 @@
         <v>7</v>
       </c>
       <c r="B1740" t="s">
-        <v>5846</v>
-      </c>
-      <c r="C1740" t="s">
-        <v>5847</v>
+        <v>5835</v>
       </c>
       <c r="D1740" t="s">
-        <v>5848</v>
+        <v>5836</v>
       </c>
       <c r="E1740" t="s">
-        <v>5849</v>
+        <v>5837</v>
       </c>
       <c r="F1740" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G1740" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1741" spans="1:7" x14ac:dyDescent="0.25">
@@ -58956,19 +58947,22 @@
         <v>7</v>
       </c>
       <c r="B1741" t="s">
-        <v>5835</v>
+        <v>5856</v>
+      </c>
+      <c r="C1741" t="s">
+        <v>5857</v>
       </c>
       <c r="D1741" t="s">
-        <v>5836</v>
+        <v>5858</v>
       </c>
       <c r="E1741" t="s">
-        <v>5837</v>
+        <v>5859</v>
       </c>
       <c r="F1741" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G1741" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1742" spans="1:7" x14ac:dyDescent="0.25">
@@ -58976,16 +58970,16 @@
         <v>7</v>
       </c>
       <c r="B1742" t="s">
-        <v>5856</v>
+        <v>5863</v>
       </c>
       <c r="C1742" t="s">
-        <v>5857</v>
+        <v>5864</v>
       </c>
       <c r="D1742" t="s">
-        <v>5858</v>
+        <v>5865</v>
       </c>
       <c r="E1742" t="s">
-        <v>5859</v>
+        <v>5866</v>
       </c>
       <c r="F1742" t="s">
         <v>12</v>
@@ -58999,16 +58993,16 @@
         <v>7</v>
       </c>
       <c r="B1743" t="s">
-        <v>5863</v>
+        <v>5867</v>
       </c>
       <c r="C1743" t="s">
-        <v>5864</v>
+        <v>5868</v>
       </c>
       <c r="D1743" t="s">
-        <v>5865</v>
+        <v>5869</v>
       </c>
       <c r="E1743" t="s">
-        <v>5866</v>
+        <v>5870</v>
       </c>
       <c r="F1743" t="s">
         <v>12</v>
@@ -59022,16 +59016,16 @@
         <v>7</v>
       </c>
       <c r="B1744" t="s">
-        <v>5867</v>
+        <v>5871</v>
       </c>
       <c r="C1744" t="s">
-        <v>5868</v>
+        <v>5872</v>
       </c>
       <c r="D1744" t="s">
-        <v>5869</v>
+        <v>5873</v>
       </c>
       <c r="E1744" t="s">
-        <v>5870</v>
+        <v>5874</v>
       </c>
       <c r="F1744" t="s">
         <v>12</v>
@@ -59045,16 +59039,16 @@
         <v>7</v>
       </c>
       <c r="B1745" t="s">
-        <v>5871</v>
+        <v>5875</v>
       </c>
       <c r="C1745" t="s">
-        <v>5872</v>
+        <v>5876</v>
       </c>
       <c r="D1745" t="s">
-        <v>5873</v>
+        <v>5877</v>
       </c>
       <c r="E1745" t="s">
-        <v>5874</v>
+        <v>5878</v>
       </c>
       <c r="F1745" t="s">
         <v>12</v>
@@ -59068,16 +59062,16 @@
         <v>7</v>
       </c>
       <c r="B1746" t="s">
-        <v>5875</v>
+        <v>3688</v>
       </c>
       <c r="C1746" t="s">
-        <v>5876</v>
+        <v>3689</v>
       </c>
       <c r="D1746" t="s">
-        <v>5877</v>
+        <v>6567</v>
       </c>
       <c r="E1746" t="s">
-        <v>5878</v>
+        <v>3690</v>
       </c>
       <c r="F1746" t="s">
         <v>12</v>
@@ -59091,16 +59085,16 @@
         <v>7</v>
       </c>
       <c r="B1747" t="s">
-        <v>3688</v>
+        <v>5879</v>
       </c>
       <c r="C1747" t="s">
-        <v>3689</v>
+        <v>5880</v>
       </c>
       <c r="D1747" t="s">
-        <v>6567</v>
+        <v>5881</v>
       </c>
       <c r="E1747" t="s">
-        <v>3690</v>
+        <v>5882</v>
       </c>
       <c r="F1747" t="s">
         <v>12</v>
@@ -59114,19 +59108,16 @@
         <v>7</v>
       </c>
       <c r="B1748" t="s">
-        <v>5879</v>
-      </c>
-      <c r="C1748" t="s">
-        <v>5880</v>
+        <v>5850</v>
       </c>
       <c r="D1748" t="s">
-        <v>5881</v>
+        <v>5851</v>
       </c>
       <c r="E1748" t="s">
-        <v>5882</v>
+        <v>5852</v>
       </c>
       <c r="F1748" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G1748" t="s">
         <v>13</v>
@@ -59137,16 +59128,19 @@
         <v>7</v>
       </c>
       <c r="B1749" t="s">
-        <v>5850</v>
+        <v>5886</v>
+      </c>
+      <c r="C1749" t="s">
+        <v>5887</v>
       </c>
       <c r="D1749" t="s">
-        <v>5851</v>
+        <v>5888</v>
       </c>
       <c r="E1749" t="s">
-        <v>5852</v>
+        <v>5889</v>
       </c>
       <c r="F1749" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G1749" t="s">
         <v>13</v>
@@ -59157,16 +59151,16 @@
         <v>7</v>
       </c>
       <c r="B1750" t="s">
-        <v>5886</v>
+        <v>5890</v>
       </c>
       <c r="C1750" t="s">
-        <v>5887</v>
+        <v>5891</v>
       </c>
       <c r="D1750" t="s">
-        <v>5888</v>
+        <v>5892</v>
       </c>
       <c r="E1750" t="s">
-        <v>5889</v>
+        <v>5893</v>
       </c>
       <c r="F1750" t="s">
         <v>12</v>
@@ -59180,16 +59174,16 @@
         <v>7</v>
       </c>
       <c r="B1751" t="s">
-        <v>5890</v>
+        <v>5894</v>
       </c>
       <c r="C1751" t="s">
-        <v>5891</v>
+        <v>5895</v>
       </c>
       <c r="D1751" t="s">
-        <v>5892</v>
+        <v>5896</v>
       </c>
       <c r="E1751" t="s">
-        <v>5893</v>
+        <v>5897</v>
       </c>
       <c r="F1751" t="s">
         <v>12</v>
@@ -59203,16 +59197,16 @@
         <v>7</v>
       </c>
       <c r="B1752" t="s">
-        <v>5894</v>
+        <v>5901</v>
       </c>
       <c r="C1752" t="s">
-        <v>5895</v>
+        <v>5902</v>
       </c>
       <c r="D1752" t="s">
-        <v>5896</v>
+        <v>5903</v>
       </c>
       <c r="E1752" t="s">
-        <v>5897</v>
+        <v>5904</v>
       </c>
       <c r="F1752" t="s">
         <v>12</v>
@@ -59226,16 +59220,16 @@
         <v>7</v>
       </c>
       <c r="B1753" t="s">
-        <v>5901</v>
+        <v>5905</v>
       </c>
       <c r="C1753" t="s">
-        <v>5902</v>
+        <v>5906</v>
       </c>
       <c r="D1753" t="s">
-        <v>5903</v>
+        <v>5907</v>
       </c>
       <c r="E1753" t="s">
-        <v>5904</v>
+        <v>5908</v>
       </c>
       <c r="F1753" t="s">
         <v>12</v>
@@ -59249,16 +59243,16 @@
         <v>7</v>
       </c>
       <c r="B1754" t="s">
-        <v>5905</v>
+        <v>5909</v>
       </c>
       <c r="C1754" t="s">
-        <v>5906</v>
+        <v>5910</v>
       </c>
       <c r="D1754" t="s">
-        <v>5907</v>
+        <v>5911</v>
       </c>
       <c r="E1754" t="s">
-        <v>5908</v>
+        <v>5912</v>
       </c>
       <c r="F1754" t="s">
         <v>12</v>
@@ -59272,19 +59266,16 @@
         <v>7</v>
       </c>
       <c r="B1755" t="s">
-        <v>5909</v>
-      </c>
-      <c r="C1755" t="s">
-        <v>5910</v>
+        <v>5883</v>
       </c>
       <c r="D1755" t="s">
-        <v>5911</v>
+        <v>5884</v>
       </c>
       <c r="E1755" t="s">
-        <v>5912</v>
+        <v>5885</v>
       </c>
       <c r="F1755" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G1755" t="s">
         <v>13</v>
@@ -59295,19 +59286,22 @@
         <v>7</v>
       </c>
       <c r="B1756" t="s">
-        <v>5883</v>
+        <v>5916</v>
+      </c>
+      <c r="C1756" t="s">
+        <v>5917</v>
       </c>
       <c r="D1756" t="s">
-        <v>5884</v>
+        <v>5918</v>
       </c>
       <c r="E1756" t="s">
-        <v>5885</v>
+        <v>5919</v>
       </c>
       <c r="F1756" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G1756" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1757" spans="1:7" x14ac:dyDescent="0.25">
@@ -59315,22 +59309,22 @@
         <v>7</v>
       </c>
       <c r="B1757" t="s">
-        <v>5916</v>
+        <v>5920</v>
       </c>
       <c r="C1757" t="s">
-        <v>5917</v>
+        <v>5921</v>
       </c>
       <c r="D1757" t="s">
-        <v>5918</v>
+        <v>5922</v>
       </c>
       <c r="E1757" t="s">
-        <v>5919</v>
+        <v>5923</v>
       </c>
       <c r="F1757" t="s">
         <v>12</v>
       </c>
       <c r="G1757" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1758" spans="1:7" x14ac:dyDescent="0.25">
@@ -59338,16 +59332,16 @@
         <v>7</v>
       </c>
       <c r="B1758" t="s">
-        <v>5920</v>
+        <v>5924</v>
       </c>
       <c r="C1758" t="s">
-        <v>5921</v>
+        <v>5925</v>
       </c>
       <c r="D1758" t="s">
-        <v>5922</v>
+        <v>5926</v>
       </c>
       <c r="E1758" t="s">
-        <v>5923</v>
+        <v>5927</v>
       </c>
       <c r="F1758" t="s">
         <v>12</v>
@@ -59361,16 +59355,16 @@
         <v>7</v>
       </c>
       <c r="B1759" t="s">
-        <v>5924</v>
+        <v>4484</v>
       </c>
       <c r="C1759" t="s">
-        <v>5925</v>
+        <v>4485</v>
       </c>
       <c r="D1759" t="s">
-        <v>5926</v>
+        <v>6568</v>
       </c>
       <c r="E1759" t="s">
-        <v>5927</v>
+        <v>4486</v>
       </c>
       <c r="F1759" t="s">
         <v>12</v>
@@ -59384,16 +59378,16 @@
         <v>7</v>
       </c>
       <c r="B1760" t="s">
-        <v>4484</v>
+        <v>5928</v>
       </c>
       <c r="C1760" t="s">
-        <v>4485</v>
+        <v>5929</v>
       </c>
       <c r="D1760" t="s">
-        <v>6568</v>
+        <v>5930</v>
       </c>
       <c r="E1760" t="s">
-        <v>4486</v>
+        <v>5931</v>
       </c>
       <c r="F1760" t="s">
         <v>12</v>
@@ -59407,16 +59401,16 @@
         <v>7</v>
       </c>
       <c r="B1761" t="s">
-        <v>5928</v>
+        <v>5932</v>
       </c>
       <c r="C1761" t="s">
-        <v>5929</v>
+        <v>5933</v>
       </c>
       <c r="D1761" t="s">
-        <v>5930</v>
+        <v>5934</v>
       </c>
       <c r="E1761" t="s">
-        <v>5931</v>
+        <v>5935</v>
       </c>
       <c r="F1761" t="s">
         <v>12</v>
@@ -59430,16 +59424,16 @@
         <v>7</v>
       </c>
       <c r="B1762" t="s">
-        <v>5932</v>
+        <v>5936</v>
       </c>
       <c r="C1762" t="s">
-        <v>5933</v>
+        <v>5937</v>
       </c>
       <c r="D1762" t="s">
-        <v>5934</v>
+        <v>5938</v>
       </c>
       <c r="E1762" t="s">
-        <v>5935</v>
+        <v>5939</v>
       </c>
       <c r="F1762" t="s">
         <v>12</v>
@@ -59453,16 +59447,16 @@
         <v>7</v>
       </c>
       <c r="B1763" t="s">
-        <v>5936</v>
+        <v>4949</v>
       </c>
       <c r="C1763" t="s">
-        <v>5937</v>
+        <v>4950</v>
       </c>
       <c r="D1763" t="s">
-        <v>5938</v>
+        <v>6569</v>
       </c>
       <c r="E1763" t="s">
-        <v>5939</v>
+        <v>4951</v>
       </c>
       <c r="F1763" t="s">
         <v>12</v>
@@ -59476,16 +59470,16 @@
         <v>7</v>
       </c>
       <c r="B1764" t="s">
-        <v>4949</v>
+        <v>5940</v>
       </c>
       <c r="C1764" t="s">
-        <v>4950</v>
+        <v>5941</v>
       </c>
       <c r="D1764" t="s">
-        <v>6569</v>
+        <v>5942</v>
       </c>
       <c r="E1764" t="s">
-        <v>4951</v>
+        <v>5943</v>
       </c>
       <c r="F1764" t="s">
         <v>12</v>
@@ -59499,22 +59493,19 @@
         <v>7</v>
       </c>
       <c r="B1765" t="s">
-        <v>5940</v>
-      </c>
-      <c r="C1765" t="s">
-        <v>5941</v>
+        <v>5913</v>
       </c>
       <c r="D1765" t="s">
-        <v>5942</v>
+        <v>5914</v>
       </c>
       <c r="E1765" t="s">
-        <v>5943</v>
+        <v>5915</v>
       </c>
       <c r="F1765" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G1765" t="s">
-        <v>13</v>
+        <v>6791</v>
       </c>
     </row>
     <row r="1766" spans="1:7" x14ac:dyDescent="0.25">
@@ -59522,19 +59513,22 @@
         <v>7</v>
       </c>
       <c r="B1766" t="s">
-        <v>5913</v>
+        <v>5947</v>
+      </c>
+      <c r="C1766" t="s">
+        <v>5948</v>
       </c>
       <c r="D1766" t="s">
-        <v>5914</v>
+        <v>5949</v>
       </c>
       <c r="E1766" t="s">
-        <v>5915</v>
+        <v>5950</v>
       </c>
       <c r="F1766" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G1766" t="s">
-        <v>6791</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1767" spans="1:7" x14ac:dyDescent="0.25">
@@ -59542,19 +59536,16 @@
         <v>7</v>
       </c>
       <c r="B1767" t="s">
-        <v>5947</v>
-      </c>
-      <c r="C1767" t="s">
-        <v>5948</v>
+        <v>5944</v>
       </c>
       <c r="D1767" t="s">
-        <v>5949</v>
+        <v>5945</v>
       </c>
       <c r="E1767" t="s">
-        <v>5950</v>
+        <v>5946</v>
       </c>
       <c r="F1767" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G1767" t="s">
         <v>13</v>
@@ -59565,16 +59556,19 @@
         <v>7</v>
       </c>
       <c r="B1768" t="s">
-        <v>5944</v>
+        <v>5954</v>
+      </c>
+      <c r="C1768" t="s">
+        <v>5955</v>
       </c>
       <c r="D1768" t="s">
-        <v>5945</v>
+        <v>5956</v>
       </c>
       <c r="E1768" t="s">
-        <v>5946</v>
+        <v>5957</v>
       </c>
       <c r="F1768" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G1768" t="s">
         <v>13</v>
@@ -59585,22 +59579,22 @@
         <v>7</v>
       </c>
       <c r="B1769" t="s">
-        <v>5954</v>
+        <v>5958</v>
       </c>
       <c r="C1769" t="s">
-        <v>5955</v>
+        <v>5959</v>
       </c>
       <c r="D1769" t="s">
-        <v>5956</v>
+        <v>5960</v>
       </c>
       <c r="E1769" t="s">
-        <v>5957</v>
+        <v>5961</v>
       </c>
       <c r="F1769" t="s">
         <v>12</v>
       </c>
       <c r="G1769" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1770" spans="1:7" x14ac:dyDescent="0.25">
@@ -59608,22 +59602,22 @@
         <v>7</v>
       </c>
       <c r="B1770" t="s">
-        <v>5958</v>
+        <v>5962</v>
       </c>
       <c r="C1770" t="s">
-        <v>5959</v>
+        <v>5963</v>
       </c>
       <c r="D1770" t="s">
-        <v>5960</v>
+        <v>5964</v>
       </c>
       <c r="E1770" t="s">
-        <v>5961</v>
+        <v>5965</v>
       </c>
       <c r="F1770" t="s">
         <v>12</v>
       </c>
       <c r="G1770" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1771" spans="1:7" x14ac:dyDescent="0.25">
@@ -59631,16 +59625,16 @@
         <v>7</v>
       </c>
       <c r="B1771" t="s">
-        <v>5962</v>
+        <v>5966</v>
       </c>
       <c r="C1771" t="s">
-        <v>5963</v>
+        <v>5967</v>
       </c>
       <c r="D1771" t="s">
-        <v>5964</v>
+        <v>5968</v>
       </c>
       <c r="E1771" t="s">
-        <v>5965</v>
+        <v>5969</v>
       </c>
       <c r="F1771" t="s">
         <v>12</v>
@@ -59654,16 +59648,16 @@
         <v>7</v>
       </c>
       <c r="B1772" t="s">
-        <v>5966</v>
+        <v>5970</v>
       </c>
       <c r="C1772" t="s">
-        <v>5967</v>
+        <v>5971</v>
       </c>
       <c r="D1772" t="s">
-        <v>5968</v>
+        <v>5972</v>
       </c>
       <c r="E1772" t="s">
-        <v>5969</v>
+        <v>5973</v>
       </c>
       <c r="F1772" t="s">
         <v>12</v>
@@ -59677,16 +59671,16 @@
         <v>7</v>
       </c>
       <c r="B1773" t="s">
-        <v>5970</v>
+        <v>5974</v>
       </c>
       <c r="C1773" t="s">
-        <v>5971</v>
+        <v>5975</v>
       </c>
       <c r="D1773" t="s">
-        <v>5972</v>
+        <v>5976</v>
       </c>
       <c r="E1773" t="s">
-        <v>5973</v>
+        <v>5977</v>
       </c>
       <c r="F1773" t="s">
         <v>12</v>
@@ -59700,19 +59694,16 @@
         <v>7</v>
       </c>
       <c r="B1774" t="s">
-        <v>5974</v>
-      </c>
-      <c r="C1774" t="s">
-        <v>5975</v>
+        <v>5951</v>
       </c>
       <c r="D1774" t="s">
-        <v>5976</v>
+        <v>5952</v>
       </c>
       <c r="E1774" t="s">
-        <v>5977</v>
+        <v>5953</v>
       </c>
       <c r="F1774" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G1774" t="s">
         <v>13</v>
@@ -59723,16 +59714,19 @@
         <v>7</v>
       </c>
       <c r="B1775" t="s">
-        <v>5951</v>
+        <v>5983</v>
+      </c>
+      <c r="C1775" t="s">
+        <v>5984</v>
       </c>
       <c r="D1775" t="s">
-        <v>5952</v>
+        <v>5985</v>
       </c>
       <c r="E1775" t="s">
-        <v>5953</v>
+        <v>5986</v>
       </c>
       <c r="F1775" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G1775" t="s">
         <v>13</v>
@@ -59743,16 +59737,16 @@
         <v>7</v>
       </c>
       <c r="B1776" t="s">
-        <v>5983</v>
+        <v>5987</v>
       </c>
       <c r="C1776" t="s">
-        <v>5984</v>
+        <v>5988</v>
       </c>
       <c r="D1776" t="s">
-        <v>5985</v>
+        <v>5989</v>
       </c>
       <c r="E1776" t="s">
-        <v>5986</v>
+        <v>5990</v>
       </c>
       <c r="F1776" t="s">
         <v>12</v>
@@ -59766,16 +59760,16 @@
         <v>7</v>
       </c>
       <c r="B1777" t="s">
-        <v>5987</v>
+        <v>5991</v>
       </c>
       <c r="C1777" t="s">
-        <v>5988</v>
+        <v>5992</v>
       </c>
       <c r="D1777" t="s">
-        <v>5989</v>
+        <v>5993</v>
       </c>
       <c r="E1777" t="s">
-        <v>5990</v>
+        <v>5994</v>
       </c>
       <c r="F1777" t="s">
         <v>12</v>
@@ -59786,45 +59780,45 @@
     </row>
     <row r="1778" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1778" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B1778" t="s">
-        <v>5991</v>
-      </c>
-      <c r="C1778" t="s">
-        <v>5992</v>
+        <v>5978</v>
       </c>
       <c r="D1778" t="s">
-        <v>5993</v>
+        <v>5979</v>
       </c>
       <c r="E1778" t="s">
-        <v>5994</v>
+        <v>6785</v>
       </c>
       <c r="F1778" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G1778" t="s">
-        <v>13</v>
+        <v>6257</v>
       </c>
     </row>
     <row r="1779" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1779" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B1779" t="s">
-        <v>5978</v>
+        <v>5997</v>
+      </c>
+      <c r="C1779" t="s">
+        <v>5998</v>
       </c>
       <c r="D1779" t="s">
-        <v>5979</v>
+        <v>5999</v>
       </c>
       <c r="E1779" t="s">
-        <v>6785</v>
+        <v>6000</v>
       </c>
       <c r="F1779" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G1779" t="s">
-        <v>6257</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1780" spans="1:7" x14ac:dyDescent="0.25">
@@ -59832,22 +59826,22 @@
         <v>7</v>
       </c>
       <c r="B1780" t="s">
-        <v>5997</v>
+        <v>6001</v>
       </c>
       <c r="C1780" t="s">
-        <v>5998</v>
+        <v>6002</v>
       </c>
       <c r="D1780" t="s">
-        <v>5999</v>
+        <v>6003</v>
       </c>
       <c r="E1780" t="s">
-        <v>6000</v>
+        <v>6004</v>
       </c>
       <c r="F1780" t="s">
         <v>12</v>
       </c>
       <c r="G1780" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1781" spans="1:7" x14ac:dyDescent="0.25">
@@ -59855,22 +59849,19 @@
         <v>7</v>
       </c>
       <c r="B1781" t="s">
-        <v>6001</v>
-      </c>
-      <c r="C1781" t="s">
-        <v>6002</v>
+        <v>5995</v>
       </c>
       <c r="D1781" t="s">
-        <v>6003</v>
+        <v>6570</v>
       </c>
       <c r="E1781" t="s">
-        <v>6004</v>
+        <v>5996</v>
       </c>
       <c r="F1781" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G1781" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1782" spans="1:7" x14ac:dyDescent="0.25">
@@ -59878,16 +59869,19 @@
         <v>7</v>
       </c>
       <c r="B1782" t="s">
-        <v>5995</v>
+        <v>6007</v>
+      </c>
+      <c r="C1782" t="s">
+        <v>6008</v>
       </c>
       <c r="D1782" t="s">
-        <v>6570</v>
+        <v>6009</v>
       </c>
       <c r="E1782" t="s">
-        <v>5996</v>
+        <v>6010</v>
       </c>
       <c r="F1782" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G1782" t="s">
         <v>13</v>
@@ -59898,16 +59892,16 @@
         <v>7</v>
       </c>
       <c r="B1783" t="s">
-        <v>6007</v>
+        <v>6011</v>
       </c>
       <c r="C1783" t="s">
-        <v>6008</v>
+        <v>6012</v>
       </c>
       <c r="D1783" t="s">
-        <v>6009</v>
+        <v>6013</v>
       </c>
       <c r="E1783" t="s">
-        <v>6010</v>
+        <v>6014</v>
       </c>
       <c r="F1783" t="s">
         <v>12</v>
@@ -59921,16 +59915,16 @@
         <v>7</v>
       </c>
       <c r="B1784" t="s">
-        <v>6011</v>
+        <v>6015</v>
       </c>
       <c r="C1784" t="s">
-        <v>6012</v>
+        <v>6016</v>
       </c>
       <c r="D1784" t="s">
-        <v>6013</v>
+        <v>6017</v>
       </c>
       <c r="E1784" t="s">
-        <v>6014</v>
+        <v>6018</v>
       </c>
       <c r="F1784" t="s">
         <v>12</v>
@@ -59944,16 +59938,13 @@
         <v>7</v>
       </c>
       <c r="B1785" t="s">
-        <v>6015</v>
-      </c>
-      <c r="C1785" t="s">
-        <v>6016</v>
+        <v>6019</v>
       </c>
       <c r="D1785" t="s">
-        <v>6017</v>
+        <v>6020</v>
       </c>
       <c r="E1785" t="s">
-        <v>6018</v>
+        <v>6021</v>
       </c>
       <c r="F1785" t="s">
         <v>12</v>
@@ -59967,13 +59958,16 @@
         <v>7</v>
       </c>
       <c r="B1786" t="s">
-        <v>6019</v>
+        <v>6022</v>
+      </c>
+      <c r="C1786" t="s">
+        <v>6023</v>
       </c>
       <c r="D1786" t="s">
-        <v>6020</v>
+        <v>6024</v>
       </c>
       <c r="E1786" t="s">
-        <v>6021</v>
+        <v>6025</v>
       </c>
       <c r="F1786" t="s">
         <v>12</v>
@@ -59987,16 +59981,16 @@
         <v>7</v>
       </c>
       <c r="B1787" t="s">
-        <v>6022</v>
+        <v>6026</v>
       </c>
       <c r="C1787" t="s">
-        <v>6023</v>
+        <v>6027</v>
       </c>
       <c r="D1787" t="s">
-        <v>6024</v>
+        <v>6028</v>
       </c>
       <c r="E1787" t="s">
-        <v>6025</v>
+        <v>6029</v>
       </c>
       <c r="F1787" t="s">
         <v>12</v>
@@ -60010,16 +60004,16 @@
         <v>7</v>
       </c>
       <c r="B1788" t="s">
-        <v>6026</v>
+        <v>6030</v>
       </c>
       <c r="C1788" t="s">
-        <v>6027</v>
+        <v>6031</v>
       </c>
       <c r="D1788" t="s">
-        <v>6028</v>
+        <v>6032</v>
       </c>
       <c r="E1788" t="s">
-        <v>6029</v>
+        <v>6033</v>
       </c>
       <c r="F1788" t="s">
         <v>12</v>
@@ -60033,19 +60027,16 @@
         <v>7</v>
       </c>
       <c r="B1789" t="s">
-        <v>6030</v>
-      </c>
-      <c r="C1789" t="s">
-        <v>6031</v>
+        <v>6005</v>
       </c>
       <c r="D1789" t="s">
-        <v>6032</v>
+        <v>6571</v>
       </c>
       <c r="E1789" t="s">
-        <v>6033</v>
+        <v>6006</v>
       </c>
       <c r="F1789" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G1789" t="s">
         <v>13</v>
@@ -60056,16 +60047,19 @@
         <v>7</v>
       </c>
       <c r="B1790" t="s">
-        <v>6005</v>
+        <v>6037</v>
+      </c>
+      <c r="C1790" t="s">
+        <v>6038</v>
       </c>
       <c r="D1790" t="s">
-        <v>6571</v>
+        <v>6039</v>
       </c>
       <c r="E1790" t="s">
-        <v>6006</v>
+        <v>6040</v>
       </c>
       <c r="F1790" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G1790" t="s">
         <v>13</v>
@@ -60076,16 +60070,16 @@
         <v>7</v>
       </c>
       <c r="B1791" t="s">
-        <v>6037</v>
+        <v>6041</v>
       </c>
       <c r="C1791" t="s">
-        <v>6038</v>
+        <v>6042</v>
       </c>
       <c r="D1791" t="s">
-        <v>6039</v>
+        <v>6043</v>
       </c>
       <c r="E1791" t="s">
-        <v>6040</v>
+        <v>6044</v>
       </c>
       <c r="F1791" t="s">
         <v>12</v>
@@ -60099,19 +60093,16 @@
         <v>7</v>
       </c>
       <c r="B1792" t="s">
-        <v>6041</v>
-      </c>
-      <c r="C1792" t="s">
-        <v>6042</v>
+        <v>6034</v>
       </c>
       <c r="D1792" t="s">
-        <v>6043</v>
+        <v>6035</v>
       </c>
       <c r="E1792" t="s">
-        <v>6044</v>
+        <v>6036</v>
       </c>
       <c r="F1792" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G1792" t="s">
         <v>13</v>
@@ -60122,19 +60113,22 @@
         <v>7</v>
       </c>
       <c r="B1793" t="s">
-        <v>6034</v>
+        <v>6047</v>
+      </c>
+      <c r="C1793" t="s">
+        <v>6048</v>
       </c>
       <c r="D1793" t="s">
-        <v>6035</v>
+        <v>6049</v>
       </c>
       <c r="E1793" t="s">
-        <v>6036</v>
+        <v>6050</v>
       </c>
       <c r="F1793" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G1793" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1794" spans="1:7" x14ac:dyDescent="0.25">
@@ -60142,59 +60136,56 @@
         <v>7</v>
       </c>
       <c r="B1794" t="s">
-        <v>6047</v>
+        <v>6051</v>
       </c>
       <c r="C1794" t="s">
-        <v>6048</v>
+        <v>6052</v>
       </c>
       <c r="D1794" t="s">
-        <v>6049</v>
+        <v>6053</v>
       </c>
       <c r="E1794" t="s">
-        <v>6050</v>
+        <v>6054</v>
       </c>
       <c r="F1794" t="s">
         <v>12</v>
       </c>
       <c r="G1794" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1795" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1795" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B1795" t="s">
-        <v>6051</v>
-      </c>
-      <c r="C1795" t="s">
-        <v>6052</v>
+        <v>6045</v>
       </c>
       <c r="D1795" t="s">
-        <v>6053</v>
+        <v>6046</v>
       </c>
       <c r="E1795" t="s">
-        <v>6054</v>
+        <v>6786</v>
       </c>
       <c r="F1795" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G1795" t="s">
-        <v>13</v>
+        <v>6257</v>
       </c>
     </row>
     <row r="1796" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1796" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B1796" t="s">
-        <v>6045</v>
+        <v>6055</v>
       </c>
       <c r="D1796" t="s">
-        <v>6046</v>
+        <v>6056</v>
       </c>
       <c r="E1796" t="s">
-        <v>6786</v>
+        <v>6057</v>
       </c>
       <c r="F1796" t="s">
         <v>17</v>
@@ -60208,19 +60199,22 @@
         <v>7</v>
       </c>
       <c r="B1797" t="s">
-        <v>6055</v>
+        <v>6060</v>
+      </c>
+      <c r="C1797" t="s">
+        <v>6061</v>
       </c>
       <c r="D1797" t="s">
-        <v>6056</v>
+        <v>6062</v>
       </c>
       <c r="E1797" t="s">
-        <v>6057</v>
+        <v>6063</v>
       </c>
       <c r="F1797" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G1797" t="s">
-        <v>6257</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1798" spans="1:7" x14ac:dyDescent="0.25">
@@ -60228,16 +60222,13 @@
         <v>7</v>
       </c>
       <c r="B1798" t="s">
-        <v>6060</v>
-      </c>
-      <c r="C1798" t="s">
-        <v>6061</v>
+        <v>6372</v>
       </c>
       <c r="D1798" t="s">
-        <v>6062</v>
+        <v>6373</v>
       </c>
       <c r="E1798" t="s">
-        <v>6063</v>
+        <v>6374</v>
       </c>
       <c r="F1798" t="s">
         <v>12</v>
@@ -60251,13 +60242,16 @@
         <v>7</v>
       </c>
       <c r="B1799" t="s">
-        <v>6372</v>
+        <v>6064</v>
+      </c>
+      <c r="C1799" t="s">
+        <v>6065</v>
       </c>
       <c r="D1799" t="s">
-        <v>6373</v>
+        <v>6066</v>
       </c>
       <c r="E1799" t="s">
-        <v>6374</v>
+        <v>6067</v>
       </c>
       <c r="F1799" t="s">
         <v>12</v>
@@ -60271,16 +60265,16 @@
         <v>7</v>
       </c>
       <c r="B1800" t="s">
-        <v>6064</v>
+        <v>6068</v>
       </c>
       <c r="C1800" t="s">
-        <v>6065</v>
+        <v>6069</v>
       </c>
       <c r="D1800" t="s">
-        <v>6066</v>
+        <v>6070</v>
       </c>
       <c r="E1800" t="s">
-        <v>6067</v>
+        <v>6071</v>
       </c>
       <c r="F1800" t="s">
         <v>12</v>
@@ -60291,45 +60285,42 @@
     </row>
     <row r="1801" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1801" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B1801" t="s">
-        <v>6068</v>
-      </c>
-      <c r="C1801" t="s">
-        <v>6069</v>
+        <v>6058</v>
       </c>
       <c r="D1801" t="s">
-        <v>6070</v>
+        <v>6059</v>
       </c>
       <c r="E1801" t="s">
-        <v>6071</v>
+        <v>6787</v>
       </c>
       <c r="F1801" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G1801" t="s">
-        <v>13</v>
+        <v>6257</v>
       </c>
     </row>
     <row r="1802" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1802" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B1802" t="s">
-        <v>6058</v>
+        <v>6072</v>
       </c>
       <c r="D1802" t="s">
-        <v>6059</v>
+        <v>6073</v>
       </c>
       <c r="E1802" t="s">
-        <v>6787</v>
+        <v>6074</v>
       </c>
       <c r="F1802" t="s">
         <v>17</v>
       </c>
       <c r="G1802" t="s">
-        <v>6257</v>
+        <v>6791</v>
       </c>
     </row>
     <row r="1803" spans="1:7" x14ac:dyDescent="0.25">
@@ -60337,19 +60328,19 @@
         <v>7</v>
       </c>
       <c r="B1803" t="s">
-        <v>6072</v>
+        <v>6075</v>
       </c>
       <c r="D1803" t="s">
-        <v>6073</v>
+        <v>6076</v>
       </c>
       <c r="E1803" t="s">
-        <v>6074</v>
+        <v>6077</v>
       </c>
       <c r="F1803" t="s">
         <v>17</v>
       </c>
       <c r="G1803" t="s">
-        <v>6791</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1804" spans="1:7" x14ac:dyDescent="0.25">
@@ -60357,19 +60348,19 @@
         <v>7</v>
       </c>
       <c r="B1804" t="s">
-        <v>6075</v>
+        <v>6304</v>
       </c>
       <c r="D1804" t="s">
-        <v>6076</v>
+        <v>6305</v>
       </c>
       <c r="E1804" t="s">
-        <v>6077</v>
+        <v>6306</v>
       </c>
       <c r="F1804" t="s">
         <v>17</v>
       </c>
       <c r="G1804" t="s">
-        <v>13</v>
+        <v>6257</v>
       </c>
     </row>
     <row r="1805" spans="1:7" x14ac:dyDescent="0.25">
@@ -60377,19 +60368,22 @@
         <v>7</v>
       </c>
       <c r="B1805" t="s">
-        <v>6304</v>
+        <v>6081</v>
+      </c>
+      <c r="C1805" t="s">
+        <v>6082</v>
       </c>
       <c r="D1805" t="s">
-        <v>6305</v>
+        <v>6083</v>
       </c>
       <c r="E1805" t="s">
-        <v>6306</v>
+        <v>6084</v>
       </c>
       <c r="F1805" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G1805" t="s">
-        <v>6257</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1806" spans="1:7" x14ac:dyDescent="0.25">
@@ -60397,16 +60391,16 @@
         <v>7</v>
       </c>
       <c r="B1806" t="s">
-        <v>6081</v>
+        <v>6085</v>
       </c>
       <c r="C1806" t="s">
-        <v>6082</v>
+        <v>6086</v>
       </c>
       <c r="D1806" t="s">
-        <v>6083</v>
+        <v>6087</v>
       </c>
       <c r="E1806" t="s">
-        <v>6084</v>
+        <v>6088</v>
       </c>
       <c r="F1806" t="s">
         <v>12</v>
@@ -60420,22 +60414,22 @@
         <v>7</v>
       </c>
       <c r="B1807" t="s">
-        <v>6085</v>
+        <v>6089</v>
       </c>
       <c r="C1807" t="s">
-        <v>6086</v>
+        <v>6090</v>
       </c>
       <c r="D1807" t="s">
-        <v>6087</v>
+        <v>6091</v>
       </c>
       <c r="E1807" t="s">
-        <v>6088</v>
+        <v>6092</v>
       </c>
       <c r="F1807" t="s">
         <v>12</v>
       </c>
       <c r="G1807" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1808" spans="1:7" x14ac:dyDescent="0.25">
@@ -60443,22 +60437,19 @@
         <v>7</v>
       </c>
       <c r="B1808" t="s">
-        <v>6089</v>
-      </c>
-      <c r="C1808" t="s">
-        <v>6090</v>
+        <v>6078</v>
       </c>
       <c r="D1808" t="s">
-        <v>6091</v>
+        <v>6079</v>
       </c>
       <c r="E1808" t="s">
-        <v>6092</v>
+        <v>6080</v>
       </c>
       <c r="F1808" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G1808" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1809" spans="1:7" x14ac:dyDescent="0.25">
@@ -60466,13 +60457,13 @@
         <v>7</v>
       </c>
       <c r="B1809" t="s">
-        <v>6078</v>
+        <v>6093</v>
       </c>
       <c r="D1809" t="s">
-        <v>6079</v>
+        <v>6572</v>
       </c>
       <c r="E1809" t="s">
-        <v>6080</v>
+        <v>6094</v>
       </c>
       <c r="F1809" t="s">
         <v>17</v>
@@ -60486,16 +60477,19 @@
         <v>7</v>
       </c>
       <c r="B1810" t="s">
-        <v>6093</v>
+        <v>6097</v>
+      </c>
+      <c r="C1810" t="s">
+        <v>6098</v>
       </c>
       <c r="D1810" t="s">
-        <v>6572</v>
+        <v>6099</v>
       </c>
       <c r="E1810" t="s">
-        <v>6094</v>
+        <v>6100</v>
       </c>
       <c r="F1810" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G1810" t="s">
         <v>13</v>
@@ -60506,16 +60500,16 @@
         <v>7</v>
       </c>
       <c r="B1811" t="s">
-        <v>6097</v>
+        <v>6101</v>
       </c>
       <c r="C1811" t="s">
-        <v>6098</v>
+        <v>6102</v>
       </c>
       <c r="D1811" t="s">
-        <v>6099</v>
+        <v>6103</v>
       </c>
       <c r="E1811" t="s">
-        <v>6100</v>
+        <v>6104</v>
       </c>
       <c r="F1811" t="s">
         <v>12</v>
@@ -60529,22 +60523,19 @@
         <v>7</v>
       </c>
       <c r="B1812" t="s">
-        <v>6101</v>
-      </c>
-      <c r="C1812" t="s">
-        <v>6102</v>
+        <v>6105</v>
       </c>
       <c r="D1812" t="s">
-        <v>6103</v>
+        <v>6106</v>
       </c>
       <c r="E1812" t="s">
-        <v>6104</v>
+        <v>6107</v>
       </c>
       <c r="F1812" t="s">
         <v>12</v>
       </c>
       <c r="G1812" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1813" spans="1:7" x14ac:dyDescent="0.25">
@@ -60552,59 +60543,62 @@
         <v>7</v>
       </c>
       <c r="B1813" t="s">
-        <v>6105</v>
+        <v>6108</v>
       </c>
       <c r="D1813" t="s">
-        <v>6106</v>
+        <v>6109</v>
       </c>
       <c r="E1813" t="s">
-        <v>6107</v>
+        <v>6110</v>
       </c>
       <c r="F1813" t="s">
         <v>12</v>
       </c>
       <c r="G1813" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1814" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1814" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B1814" t="s">
-        <v>6108</v>
+        <v>6095</v>
       </c>
       <c r="D1814" t="s">
-        <v>6109</v>
+        <v>6096</v>
       </c>
       <c r="E1814" t="s">
-        <v>6110</v>
+        <v>6788</v>
       </c>
       <c r="F1814" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G1814" t="s">
-        <v>13</v>
+        <v>6257</v>
       </c>
     </row>
     <row r="1815" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1815" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B1815" t="s">
-        <v>6095</v>
+        <v>6114</v>
+      </c>
+      <c r="C1815" t="s">
+        <v>6115</v>
       </c>
       <c r="D1815" t="s">
-        <v>6096</v>
+        <v>6116</v>
       </c>
       <c r="E1815" t="s">
-        <v>6788</v>
+        <v>6117</v>
       </c>
       <c r="F1815" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G1815" t="s">
-        <v>6257</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1816" spans="1:7" x14ac:dyDescent="0.25">
@@ -60612,16 +60606,13 @@
         <v>7</v>
       </c>
       <c r="B1816" t="s">
-        <v>6114</v>
-      </c>
-      <c r="C1816" t="s">
-        <v>6115</v>
+        <v>6118</v>
       </c>
       <c r="D1816" t="s">
-        <v>6116</v>
+        <v>6119</v>
       </c>
       <c r="E1816" t="s">
-        <v>6117</v>
+        <v>6120</v>
       </c>
       <c r="F1816" t="s">
         <v>12</v>
@@ -60635,19 +60626,19 @@
         <v>7</v>
       </c>
       <c r="B1817" t="s">
-        <v>6118</v>
+        <v>6111</v>
       </c>
       <c r="D1817" t="s">
-        <v>6119</v>
+        <v>6112</v>
       </c>
       <c r="E1817" t="s">
-        <v>6120</v>
+        <v>6113</v>
       </c>
       <c r="F1817" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G1817" t="s">
-        <v>13</v>
+        <v>6257</v>
       </c>
     </row>
     <row r="1818" spans="1:7" x14ac:dyDescent="0.25">
@@ -60655,19 +60646,22 @@
         <v>7</v>
       </c>
       <c r="B1818" t="s">
-        <v>6111</v>
+        <v>6124</v>
+      </c>
+      <c r="C1818" t="s">
+        <v>6125</v>
       </c>
       <c r="D1818" t="s">
-        <v>6112</v>
+        <v>6126</v>
       </c>
       <c r="E1818" t="s">
-        <v>6113</v>
+        <v>6127</v>
       </c>
       <c r="F1818" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G1818" t="s">
-        <v>6257</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1819" spans="1:7" x14ac:dyDescent="0.25">
@@ -60675,16 +60669,16 @@
         <v>7</v>
       </c>
       <c r="B1819" t="s">
-        <v>6124</v>
+        <v>6128</v>
       </c>
       <c r="C1819" t="s">
-        <v>6125</v>
+        <v>6129</v>
       </c>
       <c r="D1819" t="s">
-        <v>6126</v>
+        <v>6130</v>
       </c>
       <c r="E1819" t="s">
-        <v>6127</v>
+        <v>6131</v>
       </c>
       <c r="F1819" t="s">
         <v>12</v>
@@ -60698,16 +60692,16 @@
         <v>7</v>
       </c>
       <c r="B1820" t="s">
-        <v>6128</v>
+        <v>6132</v>
       </c>
       <c r="C1820" t="s">
-        <v>6129</v>
+        <v>6133</v>
       </c>
       <c r="D1820" t="s">
-        <v>6130</v>
+        <v>6134</v>
       </c>
       <c r="E1820" t="s">
-        <v>6131</v>
+        <v>6135</v>
       </c>
       <c r="F1820" t="s">
         <v>12</v>
@@ -60721,16 +60715,16 @@
         <v>7</v>
       </c>
       <c r="B1821" t="s">
-        <v>6132</v>
+        <v>6136</v>
       </c>
       <c r="C1821" t="s">
-        <v>6133</v>
+        <v>6137</v>
       </c>
       <c r="D1821" t="s">
-        <v>6134</v>
+        <v>6138</v>
       </c>
       <c r="E1821" t="s">
-        <v>6135</v>
+        <v>6139</v>
       </c>
       <c r="F1821" t="s">
         <v>12</v>
@@ -60744,22 +60738,19 @@
         <v>7</v>
       </c>
       <c r="B1822" t="s">
-        <v>6136</v>
-      </c>
-      <c r="C1822" t="s">
-        <v>6137</v>
+        <v>6121</v>
       </c>
       <c r="D1822" t="s">
-        <v>6138</v>
+        <v>6122</v>
       </c>
       <c r="E1822" t="s">
-        <v>6139</v>
+        <v>6123</v>
       </c>
       <c r="F1822" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G1822" t="s">
-        <v>13</v>
+        <v>6257</v>
       </c>
     </row>
     <row r="1823" spans="1:7" x14ac:dyDescent="0.25">
@@ -60767,19 +60758,22 @@
         <v>7</v>
       </c>
       <c r="B1823" t="s">
-        <v>6121</v>
+        <v>6144</v>
+      </c>
+      <c r="C1823" t="s">
+        <v>6145</v>
       </c>
       <c r="D1823" t="s">
-        <v>6122</v>
+        <v>6146</v>
       </c>
       <c r="E1823" t="s">
-        <v>6123</v>
+        <v>6147</v>
       </c>
       <c r="F1823" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G1823" t="s">
-        <v>6257</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1824" spans="1:7" x14ac:dyDescent="0.25">
@@ -60787,16 +60781,16 @@
         <v>7</v>
       </c>
       <c r="B1824" t="s">
-        <v>6144</v>
+        <v>6148</v>
       </c>
       <c r="C1824" t="s">
-        <v>6145</v>
+        <v>6149</v>
       </c>
       <c r="D1824" t="s">
-        <v>6146</v>
+        <v>6150</v>
       </c>
       <c r="E1824" t="s">
-        <v>6147</v>
+        <v>6151</v>
       </c>
       <c r="F1824" t="s">
         <v>12</v>
@@ -60810,16 +60804,16 @@
         <v>7</v>
       </c>
       <c r="B1825" t="s">
-        <v>6148</v>
+        <v>6152</v>
       </c>
       <c r="C1825" t="s">
-        <v>6149</v>
+        <v>6153</v>
       </c>
       <c r="D1825" t="s">
-        <v>6150</v>
+        <v>6154</v>
       </c>
       <c r="E1825" t="s">
-        <v>6151</v>
+        <v>6155</v>
       </c>
       <c r="F1825" t="s">
         <v>12</v>
@@ -60833,22 +60827,22 @@
         <v>7</v>
       </c>
       <c r="B1826" t="s">
-        <v>6152</v>
+        <v>6140</v>
       </c>
       <c r="C1826" t="s">
-        <v>6153</v>
+        <v>6141</v>
       </c>
       <c r="D1826" t="s">
-        <v>6154</v>
+        <v>6142</v>
       </c>
       <c r="E1826" t="s">
-        <v>6155</v>
+        <v>6143</v>
       </c>
       <c r="F1826" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G1826" t="s">
-        <v>13</v>
+        <v>6505</v>
       </c>
     </row>
     <row r="1827" spans="1:7" x14ac:dyDescent="0.25">
@@ -60856,22 +60850,19 @@
         <v>7</v>
       </c>
       <c r="B1827" t="s">
-        <v>6140</v>
-      </c>
-      <c r="C1827" t="s">
-        <v>6141</v>
+        <v>6156</v>
       </c>
       <c r="D1827" t="s">
-        <v>6142</v>
+        <v>6157</v>
       </c>
       <c r="E1827" t="s">
-        <v>6143</v>
+        <v>6158</v>
       </c>
       <c r="F1827" t="s">
         <v>17</v>
       </c>
       <c r="G1827" t="s">
-        <v>6505</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1828" spans="1:7" x14ac:dyDescent="0.25">
@@ -60879,16 +60870,19 @@
         <v>7</v>
       </c>
       <c r="B1828" t="s">
-        <v>6156</v>
+        <v>6159</v>
+      </c>
+      <c r="C1828" t="s">
+        <v>6160</v>
       </c>
       <c r="D1828" t="s">
-        <v>6157</v>
+        <v>6161</v>
       </c>
       <c r="E1828" t="s">
-        <v>6158</v>
+        <v>6162</v>
       </c>
       <c r="F1828" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G1828" t="s">
         <v>13</v>
@@ -60899,22 +60893,19 @@
         <v>7</v>
       </c>
       <c r="B1829" t="s">
-        <v>6159</v>
-      </c>
-      <c r="C1829" t="s">
-        <v>6160</v>
+        <v>6375</v>
       </c>
       <c r="D1829" t="s">
-        <v>6161</v>
+        <v>6376</v>
       </c>
       <c r="E1829" t="s">
-        <v>6162</v>
+        <v>6377</v>
       </c>
       <c r="F1829" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G1829" t="s">
-        <v>13</v>
+        <v>6344</v>
       </c>
     </row>
     <row r="1830" spans="1:7" x14ac:dyDescent="0.25">
@@ -60922,13 +60913,13 @@
         <v>7</v>
       </c>
       <c r="B1830" t="s">
-        <v>6375</v>
+        <v>6163</v>
       </c>
       <c r="D1830" t="s">
-        <v>6376</v>
+        <v>6164</v>
       </c>
       <c r="E1830" t="s">
-        <v>6377</v>
+        <v>6165</v>
       </c>
       <c r="F1830" t="s">
         <v>17</v>
@@ -60942,19 +60933,22 @@
         <v>7</v>
       </c>
       <c r="B1831" t="s">
-        <v>6163</v>
+        <v>6198</v>
+      </c>
+      <c r="C1831" t="s">
+        <v>6199</v>
       </c>
       <c r="D1831" t="s">
-        <v>6164</v>
+        <v>6573</v>
       </c>
       <c r="E1831" t="s">
-        <v>6165</v>
+        <v>6200</v>
       </c>
       <c r="F1831" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G1831" t="s">
-        <v>6344</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1832" spans="1:7" x14ac:dyDescent="0.25">
@@ -60962,16 +60956,16 @@
         <v>7</v>
       </c>
       <c r="B1832" t="s">
-        <v>6198</v>
+        <v>6166</v>
       </c>
       <c r="C1832" t="s">
-        <v>6199</v>
+        <v>6167</v>
       </c>
       <c r="D1832" t="s">
-        <v>6573</v>
+        <v>6574</v>
       </c>
       <c r="E1832" t="s">
-        <v>6200</v>
+        <v>6168</v>
       </c>
       <c r="F1832" t="s">
         <v>12</v>
@@ -60985,16 +60979,16 @@
         <v>7</v>
       </c>
       <c r="B1833" t="s">
-        <v>6166</v>
+        <v>6169</v>
       </c>
       <c r="C1833" t="s">
-        <v>6167</v>
+        <v>6170</v>
       </c>
       <c r="D1833" t="s">
-        <v>6574</v>
+        <v>6575</v>
       </c>
       <c r="E1833" t="s">
-        <v>6168</v>
+        <v>6171</v>
       </c>
       <c r="F1833" t="s">
         <v>12</v>
@@ -61008,16 +61002,16 @@
         <v>7</v>
       </c>
       <c r="B1834" t="s">
-        <v>6169</v>
+        <v>6172</v>
       </c>
       <c r="C1834" t="s">
-        <v>6170</v>
+        <v>6173</v>
       </c>
       <c r="D1834" t="s">
-        <v>6575</v>
+        <v>6576</v>
       </c>
       <c r="E1834" t="s">
-        <v>6171</v>
+        <v>6174</v>
       </c>
       <c r="F1834" t="s">
         <v>12</v>
@@ -61031,16 +61025,16 @@
         <v>7</v>
       </c>
       <c r="B1835" t="s">
-        <v>6172</v>
+        <v>6175</v>
       </c>
       <c r="C1835" t="s">
-        <v>6173</v>
+        <v>6176</v>
       </c>
       <c r="D1835" t="s">
-        <v>6576</v>
+        <v>6577</v>
       </c>
       <c r="E1835" t="s">
-        <v>6174</v>
+        <v>6177</v>
       </c>
       <c r="F1835" t="s">
         <v>12</v>
@@ -61054,16 +61048,16 @@
         <v>7</v>
       </c>
       <c r="B1836" t="s">
-        <v>6175</v>
+        <v>6191</v>
       </c>
       <c r="C1836" t="s">
-        <v>6176</v>
+        <v>6192</v>
       </c>
       <c r="D1836" t="s">
-        <v>6577</v>
+        <v>6578</v>
       </c>
       <c r="E1836" t="s">
-        <v>6177</v>
+        <v>6193</v>
       </c>
       <c r="F1836" t="s">
         <v>12</v>
@@ -61077,16 +61071,13 @@
         <v>7</v>
       </c>
       <c r="B1837" t="s">
-        <v>6191</v>
-      </c>
-      <c r="C1837" t="s">
-        <v>6192</v>
+        <v>6178</v>
       </c>
       <c r="D1837" t="s">
-        <v>6578</v>
+        <v>6579</v>
       </c>
       <c r="E1837" t="s">
-        <v>6193</v>
+        <v>6179</v>
       </c>
       <c r="F1837" t="s">
         <v>12</v>
@@ -61100,13 +61091,16 @@
         <v>7</v>
       </c>
       <c r="B1838" t="s">
-        <v>6178</v>
+        <v>6180</v>
+      </c>
+      <c r="C1838" t="s">
+        <v>6181</v>
       </c>
       <c r="D1838" t="s">
-        <v>6579</v>
+        <v>6580</v>
       </c>
       <c r="E1838" t="s">
-        <v>6179</v>
+        <v>6182</v>
       </c>
       <c r="F1838" t="s">
         <v>12</v>
@@ -61120,16 +61114,16 @@
         <v>7</v>
       </c>
       <c r="B1839" t="s">
-        <v>6180</v>
+        <v>6183</v>
       </c>
       <c r="C1839" t="s">
-        <v>6181</v>
+        <v>6184</v>
       </c>
       <c r="D1839" t="s">
-        <v>6580</v>
+        <v>6581</v>
       </c>
       <c r="E1839" t="s">
-        <v>6182</v>
+        <v>6185</v>
       </c>
       <c r="F1839" t="s">
         <v>12</v>
@@ -61143,16 +61137,16 @@
         <v>7</v>
       </c>
       <c r="B1840" t="s">
-        <v>6183</v>
+        <v>6186</v>
       </c>
       <c r="C1840" t="s">
-        <v>6184</v>
+        <v>6187</v>
       </c>
       <c r="D1840" t="s">
-        <v>6581</v>
+        <v>6582</v>
       </c>
       <c r="E1840" t="s">
-        <v>6185</v>
+        <v>6188</v>
       </c>
       <c r="F1840" t="s">
         <v>12</v>
@@ -61166,16 +61160,13 @@
         <v>7</v>
       </c>
       <c r="B1841" t="s">
-        <v>6186</v>
-      </c>
-      <c r="C1841" t="s">
-        <v>6187</v>
+        <v>6189</v>
       </c>
       <c r="D1841" t="s">
-        <v>6582</v>
+        <v>6583</v>
       </c>
       <c r="E1841" t="s">
-        <v>6188</v>
+        <v>6190</v>
       </c>
       <c r="F1841" t="s">
         <v>12</v>
@@ -61189,19 +61180,19 @@
         <v>7</v>
       </c>
       <c r="B1842" t="s">
-        <v>6189</v>
+        <v>6378</v>
       </c>
       <c r="D1842" t="s">
-        <v>6583</v>
+        <v>6379</v>
       </c>
       <c r="E1842" t="s">
-        <v>6190</v>
+        <v>6380</v>
       </c>
       <c r="F1842" t="s">
         <v>12</v>
       </c>
       <c r="G1842" t="s">
-        <v>13</v>
+        <v>6257</v>
       </c>
     </row>
     <row r="1843" spans="1:7" x14ac:dyDescent="0.25">
@@ -61209,19 +61200,22 @@
         <v>7</v>
       </c>
       <c r="B1843" t="s">
-        <v>6378</v>
+        <v>6201</v>
+      </c>
+      <c r="C1843" t="s">
+        <v>6202</v>
       </c>
       <c r="D1843" t="s">
-        <v>6379</v>
+        <v>6203</v>
       </c>
       <c r="E1843" t="s">
-        <v>6380</v>
+        <v>6204</v>
       </c>
       <c r="F1843" t="s">
         <v>12</v>
       </c>
       <c r="G1843" t="s">
-        <v>6257</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1844" spans="1:7" x14ac:dyDescent="0.25">
@@ -61229,16 +61223,13 @@
         <v>7</v>
       </c>
       <c r="B1844" t="s">
-        <v>6201</v>
-      </c>
-      <c r="C1844" t="s">
-        <v>6202</v>
+        <v>6205</v>
       </c>
       <c r="D1844" t="s">
-        <v>6203</v>
+        <v>6206</v>
       </c>
       <c r="E1844" t="s">
-        <v>6204</v>
+        <v>6207</v>
       </c>
       <c r="F1844" t="s">
         <v>12</v>
@@ -61252,16 +61243,19 @@
         <v>7</v>
       </c>
       <c r="B1845" t="s">
-        <v>6205</v>
+        <v>6194</v>
+      </c>
+      <c r="C1845" t="s">
+        <v>6195</v>
       </c>
       <c r="D1845" t="s">
-        <v>6206</v>
+        <v>6196</v>
       </c>
       <c r="E1845" t="s">
-        <v>6207</v>
+        <v>6197</v>
       </c>
       <c r="F1845" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G1845" t="s">
         <v>13</v>
@@ -61272,22 +61266,19 @@
         <v>7</v>
       </c>
       <c r="B1846" t="s">
-        <v>6194</v>
-      </c>
-      <c r="C1846" t="s">
-        <v>6195</v>
+        <v>6381</v>
       </c>
       <c r="D1846" t="s">
-        <v>6196</v>
+        <v>6382</v>
       </c>
       <c r="E1846" t="s">
-        <v>6197</v>
+        <v>6383</v>
       </c>
       <c r="F1846" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G1846" t="s">
-        <v>13</v>
+        <v>6257</v>
       </c>
     </row>
     <row r="1847" spans="1:7" x14ac:dyDescent="0.25">
@@ -61295,19 +61286,19 @@
         <v>7</v>
       </c>
       <c r="B1847" t="s">
-        <v>6381</v>
+        <v>6211</v>
       </c>
       <c r="D1847" t="s">
-        <v>6382</v>
+        <v>6584</v>
       </c>
       <c r="E1847" t="s">
-        <v>6383</v>
+        <v>6212</v>
       </c>
       <c r="F1847" t="s">
         <v>12</v>
       </c>
       <c r="G1847" t="s">
-        <v>6257</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1848" spans="1:7" x14ac:dyDescent="0.25">
@@ -61315,13 +61306,13 @@
         <v>7</v>
       </c>
       <c r="B1848" t="s">
-        <v>6211</v>
+        <v>6213</v>
       </c>
       <c r="D1848" t="s">
-        <v>6584</v>
+        <v>6214</v>
       </c>
       <c r="E1848" t="s">
-        <v>6212</v>
+        <v>6215</v>
       </c>
       <c r="F1848" t="s">
         <v>12</v>
@@ -61335,13 +61326,16 @@
         <v>7</v>
       </c>
       <c r="B1849" t="s">
-        <v>6213</v>
+        <v>6216</v>
+      </c>
+      <c r="C1849" t="s">
+        <v>6217</v>
       </c>
       <c r="D1849" t="s">
-        <v>6214</v>
+        <v>6218</v>
       </c>
       <c r="E1849" t="s">
-        <v>6215</v>
+        <v>6219</v>
       </c>
       <c r="F1849" t="s">
         <v>12</v>
@@ -61355,16 +61349,16 @@
         <v>7</v>
       </c>
       <c r="B1850" t="s">
-        <v>6216</v>
+        <v>6220</v>
       </c>
       <c r="C1850" t="s">
-        <v>6217</v>
+        <v>6221</v>
       </c>
       <c r="D1850" t="s">
-        <v>6218</v>
+        <v>6222</v>
       </c>
       <c r="E1850" t="s">
-        <v>6219</v>
+        <v>6223</v>
       </c>
       <c r="F1850" t="s">
         <v>12</v>
@@ -61378,16 +61372,16 @@
         <v>7</v>
       </c>
       <c r="B1851" t="s">
-        <v>6220</v>
+        <v>6224</v>
       </c>
       <c r="C1851" t="s">
-        <v>6221</v>
+        <v>6225</v>
       </c>
       <c r="D1851" t="s">
-        <v>6222</v>
+        <v>6226</v>
       </c>
       <c r="E1851" t="s">
-        <v>6223</v>
+        <v>6227</v>
       </c>
       <c r="F1851" t="s">
         <v>12</v>
@@ -61401,16 +61395,16 @@
         <v>7</v>
       </c>
       <c r="B1852" t="s">
-        <v>6224</v>
+        <v>6228</v>
       </c>
       <c r="C1852" t="s">
-        <v>6225</v>
+        <v>6229</v>
       </c>
       <c r="D1852" t="s">
-        <v>6226</v>
+        <v>6230</v>
       </c>
       <c r="E1852" t="s">
-        <v>6227</v>
+        <v>6231</v>
       </c>
       <c r="F1852" t="s">
         <v>12</v>
@@ -61424,16 +61418,16 @@
         <v>7</v>
       </c>
       <c r="B1853" t="s">
-        <v>6228</v>
+        <v>6232</v>
       </c>
       <c r="C1853" t="s">
-        <v>6229</v>
+        <v>6233</v>
       </c>
       <c r="D1853" t="s">
-        <v>6230</v>
+        <v>6234</v>
       </c>
       <c r="E1853" t="s">
-        <v>6231</v>
+        <v>6235</v>
       </c>
       <c r="F1853" t="s">
         <v>12</v>
@@ -61447,16 +61441,16 @@
         <v>7</v>
       </c>
       <c r="B1854" t="s">
-        <v>6232</v>
+        <v>6236</v>
       </c>
       <c r="C1854" t="s">
-        <v>6233</v>
+        <v>6237</v>
       </c>
       <c r="D1854" t="s">
-        <v>6234</v>
+        <v>6585</v>
       </c>
       <c r="E1854" t="s">
-        <v>6235</v>
+        <v>6238</v>
       </c>
       <c r="F1854" t="s">
         <v>12</v>
@@ -61470,16 +61464,16 @@
         <v>7</v>
       </c>
       <c r="B1855" t="s">
-        <v>6236</v>
+        <v>6239</v>
       </c>
       <c r="C1855" t="s">
-        <v>6237</v>
+        <v>6240</v>
       </c>
       <c r="D1855" t="s">
-        <v>6585</v>
+        <v>6241</v>
       </c>
       <c r="E1855" t="s">
-        <v>6238</v>
+        <v>6242</v>
       </c>
       <c r="F1855" t="s">
         <v>12</v>
@@ -61493,16 +61487,16 @@
         <v>7</v>
       </c>
       <c r="B1856" t="s">
-        <v>6239</v>
+        <v>6243</v>
       </c>
       <c r="C1856" t="s">
-        <v>6240</v>
+        <v>6244</v>
       </c>
       <c r="D1856" t="s">
-        <v>6241</v>
+        <v>6245</v>
       </c>
       <c r="E1856" t="s">
-        <v>6242</v>
+        <v>6246</v>
       </c>
       <c r="F1856" t="s">
         <v>12</v>
@@ -61516,16 +61510,16 @@
         <v>7</v>
       </c>
       <c r="B1857" t="s">
-        <v>6243</v>
+        <v>6247</v>
       </c>
       <c r="C1857" t="s">
-        <v>6244</v>
+        <v>6248</v>
       </c>
       <c r="D1857" t="s">
-        <v>6245</v>
+        <v>6249</v>
       </c>
       <c r="E1857" t="s">
-        <v>6246</v>
+        <v>6250</v>
       </c>
       <c r="F1857" t="s">
         <v>12</v>
@@ -61539,16 +61533,16 @@
         <v>7</v>
       </c>
       <c r="B1858" t="s">
-        <v>6247</v>
+        <v>6251</v>
       </c>
       <c r="C1858" t="s">
-        <v>6248</v>
+        <v>6252</v>
       </c>
       <c r="D1858" t="s">
-        <v>6249</v>
+        <v>6253</v>
       </c>
       <c r="E1858" t="s">
-        <v>6250</v>
+        <v>6254</v>
       </c>
       <c r="F1858" t="s">
         <v>12</v>
@@ -61562,41 +61556,18 @@
         <v>7</v>
       </c>
       <c r="B1859" t="s">
-        <v>6251</v>
-      </c>
-      <c r="C1859" t="s">
-        <v>6252</v>
+        <v>6208</v>
       </c>
       <c r="D1859" t="s">
-        <v>6253</v>
+        <v>6209</v>
       </c>
       <c r="E1859" t="s">
-        <v>6254</v>
+        <v>6210</v>
       </c>
       <c r="F1859" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G1859" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="1860" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1860" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1860" t="s">
-        <v>6208</v>
-      </c>
-      <c r="D1860" t="s">
-        <v>6209</v>
-      </c>
-      <c r="E1860" t="s">
-        <v>6210</v>
-      </c>
-      <c r="F1860" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1860" t="s">
         <v>13</v>
       </c>
     </row>
